--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/19,10,26 Останкино КИ и ЗПФ/дв 19,10,26 днрсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/19,10,26 Останкино КИ и ЗПФ/дв 19,10,26 днрсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\10,26\19,10,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3B2185-30E6-49A1-9A6A-5AECB85792B2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC02364B-F30F-48D2-968C-A6A155488F37}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6745,7 +6745,7 @@
     <col min="22" max="22" width="8.28515625" style="20" customWidth="1"/>
     <col min="23" max="24" width="5" customWidth="1"/>
     <col min="25" max="34" width="6" customWidth="1"/>
-    <col min="35" max="35" width="30.42578125" customWidth="1"/>
+    <col min="35" max="35" width="19.5703125" customWidth="1"/>
     <col min="36" max="51" width="7" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6789,7 +6789,9 @@
       <c r="AI1" s="8"/>
       <c r="AJ1" s="8"/>
       <c r="AK1" s="8"/>
-      <c r="AL1" s="8"/>
+      <c r="AL1" s="8">
+        <v>6500</v>
+      </c>
       <c r="AM1" s="8"/>
       <c r="AN1" s="8"/>
       <c r="AO1" s="8"/>
@@ -6844,7 +6846,9 @@
       <c r="AI2" s="8"/>
       <c r="AJ2" s="8"/>
       <c r="AK2" s="8"/>
-      <c r="AL2" s="8"/>
+      <c r="AL2" s="8">
+        <v>4500</v>
+      </c>
       <c r="AM2" s="8"/>
       <c r="AN2" s="8"/>
       <c r="AO2" s="8"/>
@@ -7060,7 +7064,10 @@
       <c r="AK4" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="AL4" s="8"/>
+      <c r="AL4" s="8">
+        <f>6*AL5</f>
+        <v>10873.622400000002</v>
+      </c>
       <c r="AM4" s="8"/>
       <c r="AN4" s="8"/>
       <c r="AO4" s="8"/>
@@ -7191,7 +7198,10 @@
         <f>SUM(AK6:AK495)</f>
         <v>4574.46</v>
       </c>
-      <c r="AL5" s="8"/>
+      <c r="AL5" s="3">
+        <f>SUM(AL6:AL495)</f>
+        <v>1812.2704000000003</v>
+      </c>
       <c r="AM5" s="8"/>
       <c r="AN5" s="8"/>
       <c r="AO5" s="8"/>
@@ -7315,7 +7325,10 @@
         <f>G6*U6</f>
         <v>0</v>
       </c>
-      <c r="AL6" s="8"/>
+      <c r="AL6" s="8">
+        <f>Q6*G6</f>
+        <v>0.87919999999999998</v>
+      </c>
       <c r="AM6" s="8"/>
       <c r="AN6" s="8"/>
       <c r="AO6" s="8"/>
@@ -7447,7 +7460,10 @@
         <f>G7*U7</f>
         <v>24</v>
       </c>
-      <c r="AL7" s="8"/>
+      <c r="AL7" s="8">
+        <f t="shared" ref="AL7:AL70" si="11">Q7*G7</f>
+        <v>16.240000000000002</v>
+      </c>
       <c r="AM7" s="8"/>
       <c r="AN7" s="8"/>
       <c r="AO7" s="8"/>
@@ -7520,7 +7536,7 @@
         <v>12</v>
       </c>
       <c r="T8" s="4">
-        <f t="shared" ref="T8:T70" si="11">ROUND(S8-U8,0)</f>
+        <f t="shared" ref="T8:T70" si="12">ROUND(S8-U8,0)</f>
         <v>12</v>
       </c>
       <c r="U8" s="4"/>
@@ -7569,10 +7585,13 @@
         <v>12</v>
       </c>
       <c r="AK8" s="8">
-        <f t="shared" ref="AK8:AK70" si="12">G8*U8</f>
-        <v>0</v>
-      </c>
-      <c r="AL8" s="8"/>
+        <f t="shared" ref="AK8:AK70" si="13">G8*U8</f>
+        <v>0</v>
+      </c>
+      <c r="AL8" s="8">
+        <f t="shared" si="11"/>
+        <v>1.5092000000000001</v>
+      </c>
       <c r="AM8" s="8"/>
       <c r="AN8" s="8"/>
       <c r="AO8" s="8"/>
@@ -7647,11 +7666,11 @@
         <v>110</v>
       </c>
       <c r="T9" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>66</v>
       </c>
       <c r="U9" s="4">
-        <f t="shared" ref="U9:U10" si="13">ROUND(S9*$U$1,0)</f>
+        <f t="shared" ref="U9:U10" si="14">ROUND(S9*$U$1,0)</f>
         <v>44</v>
       </c>
       <c r="V9" s="19"/>
@@ -7699,10 +7718,13 @@
         <v>16.5</v>
       </c>
       <c r="AK9" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>11</v>
       </c>
-      <c r="AL9" s="8"/>
+      <c r="AL9" s="8">
+        <f t="shared" si="11"/>
+        <v>8.8000000000000007</v>
+      </c>
       <c r="AM9" s="8"/>
       <c r="AN9" s="8"/>
       <c r="AO9" s="8"/>
@@ -7779,11 +7801,11 @@
         <v>2130</v>
       </c>
       <c r="T10" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1278</v>
       </c>
       <c r="U10" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>852</v>
       </c>
       <c r="V10" s="19">
@@ -7834,10 +7856,13 @@
         <v>1278</v>
       </c>
       <c r="AK10" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>852</v>
       </c>
-      <c r="AL10" s="8"/>
+      <c r="AL10" s="8">
+        <f t="shared" si="11"/>
+        <v>235.161</v>
+      </c>
       <c r="AM10" s="8"/>
       <c r="AN10" s="8"/>
       <c r="AO10" s="8"/>
@@ -7910,7 +7935,7 @@
         <v>8</v>
       </c>
       <c r="T11" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8</v>
       </c>
       <c r="U11" s="4"/>
@@ -7959,10 +7984,13 @@
         <v>8</v>
       </c>
       <c r="AK11" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL11" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL11" s="8">
+        <f t="shared" si="11"/>
+        <v>2.4818000000000002</v>
+      </c>
       <c r="AM11" s="8"/>
       <c r="AN11" s="8"/>
       <c r="AO11" s="8"/>
@@ -8035,11 +8063,11 @@
         <v>272</v>
       </c>
       <c r="T12" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>163</v>
       </c>
       <c r="U12" s="4">
-        <f t="shared" ref="U12:U14" si="14">ROUND(S12*$U$1,0)</f>
+        <f t="shared" ref="U12:U14" si="15">ROUND(S12*$U$1,0)</f>
         <v>109</v>
       </c>
       <c r="V12" s="19"/>
@@ -8087,10 +8115,13 @@
         <v>163</v>
       </c>
       <c r="AK12" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>109</v>
       </c>
-      <c r="AL12" s="8"/>
+      <c r="AL12" s="8">
+        <f t="shared" si="11"/>
+        <v>31.758999999999997</v>
+      </c>
       <c r="AM12" s="8"/>
       <c r="AN12" s="8"/>
       <c r="AO12" s="8"/>
@@ -8167,11 +8198,11 @@
         <v>830</v>
       </c>
       <c r="T13" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>498</v>
       </c>
       <c r="U13" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>332</v>
       </c>
       <c r="V13" s="19">
@@ -8222,10 +8253,13 @@
         <v>498</v>
       </c>
       <c r="AK13" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>332</v>
       </c>
-      <c r="AL13" s="8"/>
+      <c r="AL13" s="8">
+        <f t="shared" si="11"/>
+        <v>102.21459999999999</v>
+      </c>
       <c r="AM13" s="8"/>
       <c r="AN13" s="8"/>
       <c r="AO13" s="8"/>
@@ -8298,11 +8332,11 @@
         <v>118</v>
       </c>
       <c r="T14" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>71</v>
       </c>
       <c r="U14" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>47</v>
       </c>
       <c r="V14" s="19"/>
@@ -8350,10 +8384,13 @@
         <v>17.75</v>
       </c>
       <c r="AK14" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>11.75</v>
       </c>
-      <c r="AL14" s="8"/>
+      <c r="AL14" s="8">
+        <f t="shared" si="11"/>
+        <v>3.8</v>
+      </c>
       <c r="AM14" s="8"/>
       <c r="AN14" s="8"/>
       <c r="AO14" s="8"/>
@@ -8430,7 +8467,7 @@
         <v>78</v>
       </c>
       <c r="T15" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>78</v>
       </c>
       <c r="U15" s="4"/>
@@ -8479,10 +8516,13 @@
         <v>78</v>
       </c>
       <c r="AK15" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL15" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL15" s="8">
+        <f t="shared" si="11"/>
+        <v>13.6668</v>
+      </c>
       <c r="AM15" s="8"/>
       <c r="AN15" s="8"/>
       <c r="AO15" s="8"/>
@@ -8557,11 +8597,11 @@
         <v>245</v>
       </c>
       <c r="T16" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>147</v>
       </c>
       <c r="U16" s="4">
-        <f t="shared" ref="U16:U18" si="15">ROUND(S16*$U$1,0)</f>
+        <f t="shared" ref="U16:U18" si="16">ROUND(S16*$U$1,0)</f>
         <v>98</v>
       </c>
       <c r="V16" s="19"/>
@@ -8609,10 +8649,13 @@
         <v>36.75</v>
       </c>
       <c r="AK16" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>24.5</v>
       </c>
-      <c r="AL16" s="8"/>
+      <c r="AL16" s="8">
+        <f t="shared" si="11"/>
+        <v>6.55</v>
+      </c>
       <c r="AM16" s="8"/>
       <c r="AN16" s="8"/>
       <c r="AO16" s="8"/>
@@ -8684,11 +8727,11 @@
         <v>500</v>
       </c>
       <c r="T17" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>300</v>
       </c>
       <c r="U17" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>200</v>
       </c>
       <c r="V17" s="19"/>
@@ -8738,10 +8781,13 @@
         <v>120</v>
       </c>
       <c r="AK17" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>80</v>
       </c>
-      <c r="AL17" s="8"/>
+      <c r="AL17" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM17" s="8"/>
       <c r="AN17" s="8"/>
       <c r="AO17" s="8"/>
@@ -8814,11 +8860,11 @@
         <v>125</v>
       </c>
       <c r="T18" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>75</v>
       </c>
       <c r="U18" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>50</v>
       </c>
       <c r="V18" s="19"/>
@@ -8866,10 +8912,13 @@
         <v>75</v>
       </c>
       <c r="AK18" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>50</v>
       </c>
-      <c r="AL18" s="8"/>
+      <c r="AL18" s="8">
+        <f t="shared" si="11"/>
+        <v>61.370199999999997</v>
+      </c>
       <c r="AM18" s="8"/>
       <c r="AN18" s="8"/>
       <c r="AO18" s="8"/>
@@ -8937,7 +8986,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U19" s="4"/>
@@ -8988,10 +9037,13 @@
         <v>0</v>
       </c>
       <c r="AK19" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL19" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL19" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM19" s="8"/>
       <c r="AN19" s="8"/>
       <c r="AO19" s="8"/>
@@ -9061,7 +9113,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U20" s="4"/>
@@ -9112,10 +9164,13 @@
         <v>0</v>
       </c>
       <c r="AK20" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL20" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL20" s="8">
+        <f t="shared" si="11"/>
+        <v>15.280000000000001</v>
+      </c>
       <c r="AM20" s="8"/>
       <c r="AN20" s="8"/>
       <c r="AO20" s="8"/>
@@ -9190,11 +9245,11 @@
         <v>607</v>
       </c>
       <c r="T21" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>364</v>
       </c>
       <c r="U21" s="4">
-        <f t="shared" ref="U21:U22" si="16">ROUND(S21*$U$1,0)</f>
+        <f t="shared" ref="U21:U22" si="17">ROUND(S21*$U$1,0)</f>
         <v>243</v>
       </c>
       <c r="V21" s="19"/>
@@ -9242,10 +9297,13 @@
         <v>364</v>
       </c>
       <c r="AK21" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>243</v>
       </c>
-      <c r="AL21" s="8"/>
+      <c r="AL21" s="8">
+        <f t="shared" si="11"/>
+        <v>66.264399999999995</v>
+      </c>
       <c r="AM21" s="8"/>
       <c r="AN21" s="8"/>
       <c r="AO21" s="8"/>
@@ -9315,11 +9373,11 @@
         <v>400</v>
       </c>
       <c r="T22" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>240</v>
       </c>
       <c r="U22" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>160</v>
       </c>
       <c r="V22" s="19"/>
@@ -9369,10 +9427,13 @@
         <v>52.8</v>
       </c>
       <c r="AK22" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>35.200000000000003</v>
       </c>
-      <c r="AL22" s="8"/>
+      <c r="AL22" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM22" s="8"/>
       <c r="AN22" s="8"/>
       <c r="AO22" s="8"/>
@@ -9437,7 +9498,7 @@
         <v>2.8115999999999999</v>
       </c>
       <c r="R23" s="4">
-        <f t="shared" ref="R23" si="17">15*Q23-P23-O23-F23</f>
+        <f t="shared" ref="R23" si="18">15*Q23-P23-O23-F23</f>
         <v>14.928000000000001</v>
       </c>
       <c r="S23" s="4">
@@ -9445,7 +9506,7 @@
         <v>15</v>
       </c>
       <c r="T23" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>15</v>
       </c>
       <c r="U23" s="4"/>
@@ -9494,10 +9555,13 @@
         <v>15</v>
       </c>
       <c r="AK23" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL23" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL23" s="8">
+        <f t="shared" si="11"/>
+        <v>2.8115999999999999</v>
+      </c>
       <c r="AM23" s="8"/>
       <c r="AN23" s="8"/>
       <c r="AO23" s="8"/>
@@ -9565,7 +9629,7 @@
         <v>0</v>
       </c>
       <c r="T24" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U24" s="4"/>
@@ -9614,10 +9678,13 @@
         <v>0</v>
       </c>
       <c r="AK24" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL24" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL24" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM24" s="8"/>
       <c r="AN24" s="8"/>
       <c r="AO24" s="8"/>
@@ -9684,7 +9751,7 @@
         <v>61.055799999999998</v>
       </c>
       <c r="R25" s="4">
-        <f t="shared" ref="R25:R27" si="18">15*Q25-P25-O25-F25</f>
+        <f t="shared" ref="R25:R27" si="19">15*Q25-P25-O25-F25</f>
         <v>411.16199999999998</v>
       </c>
       <c r="S25" s="4">
@@ -9692,11 +9759,11 @@
         <v>411</v>
       </c>
       <c r="T25" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>247</v>
       </c>
       <c r="U25" s="4">
-        <f t="shared" ref="U25:U27" si="19">ROUND(S25*$U$1,0)</f>
+        <f t="shared" ref="U25:U27" si="20">ROUND(S25*$U$1,0)</f>
         <v>164</v>
       </c>
       <c r="V25" s="19"/>
@@ -9744,10 +9811,13 @@
         <v>247</v>
       </c>
       <c r="AK25" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>164</v>
       </c>
-      <c r="AL25" s="8"/>
+      <c r="AL25" s="8">
+        <f t="shared" si="11"/>
+        <v>61.055799999999998</v>
+      </c>
       <c r="AM25" s="8"/>
       <c r="AN25" s="8"/>
       <c r="AO25" s="8"/>
@@ -9820,11 +9890,11 @@
         <v>400</v>
       </c>
       <c r="T26" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>240</v>
       </c>
       <c r="U26" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>160</v>
       </c>
       <c r="V26" s="19" t="str">
@@ -9877,10 +9947,13 @@
         <v>21.599999999999998</v>
       </c>
       <c r="AK26" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14.399999999999999</v>
       </c>
-      <c r="AL26" s="8"/>
+      <c r="AL26" s="8">
+        <f t="shared" si="11"/>
+        <v>5.0039999999999996</v>
+      </c>
       <c r="AM26" s="8"/>
       <c r="AN26" s="8"/>
       <c r="AO26" s="8"/>
@@ -9945,7 +10018,7 @@
         <v>25.6</v>
       </c>
       <c r="R27" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>186</v>
       </c>
       <c r="S27" s="4">
@@ -9953,11 +10026,11 @@
         <v>186</v>
       </c>
       <c r="T27" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>112</v>
       </c>
       <c r="U27" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>74</v>
       </c>
       <c r="V27" s="19"/>
@@ -10005,10 +10078,13 @@
         <v>10.08</v>
       </c>
       <c r="AK27" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.66</v>
       </c>
-      <c r="AL27" s="8"/>
+      <c r="AL27" s="8">
+        <f t="shared" si="11"/>
+        <v>2.3039999999999998</v>
+      </c>
       <c r="AM27" s="8"/>
       <c r="AN27" s="8"/>
       <c r="AO27" s="8"/>
@@ -10072,7 +10148,7 @@
         <v>0</v>
       </c>
       <c r="T28" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U28" s="4"/>
@@ -10121,10 +10197,13 @@
         <v>0</v>
       </c>
       <c r="AK28" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL28" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL28" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM28" s="8"/>
       <c r="AN28" s="8"/>
       <c r="AO28" s="8"/>
@@ -10189,7 +10268,7 @@
         <v>18.399999999999999</v>
       </c>
       <c r="R29" s="4">
-        <f t="shared" ref="R29:R33" si="20">15*Q29-P29-O29-F29</f>
+        <f t="shared" ref="R29:R33" si="21">15*Q29-P29-O29-F29</f>
         <v>128</v>
       </c>
       <c r="S29" s="4">
@@ -10197,7 +10276,7 @@
         <v>145</v>
       </c>
       <c r="T29" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>87</v>
       </c>
       <c r="U29" s="4">
@@ -10254,10 +10333,13 @@
         <v>13.049999999999999</v>
       </c>
       <c r="AK29" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>8.6999999999999993</v>
       </c>
-      <c r="AL29" s="8"/>
+      <c r="AL29" s="8">
+        <f t="shared" si="11"/>
+        <v>2.76</v>
+      </c>
       <c r="AM29" s="8"/>
       <c r="AN29" s="8"/>
       <c r="AO29" s="8"/>
@@ -10329,7 +10411,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U30" s="4"/>
@@ -10380,10 +10462,13 @@
         <v>0</v>
       </c>
       <c r="AK30" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL30" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL30" s="8">
+        <f t="shared" si="11"/>
+        <v>8.3051999999999992</v>
+      </c>
       <c r="AM30" s="8"/>
       <c r="AN30" s="8"/>
       <c r="AO30" s="8"/>
@@ -10456,11 +10541,11 @@
         <v>192</v>
       </c>
       <c r="T31" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>115</v>
       </c>
       <c r="U31" s="4">
-        <f t="shared" ref="U31:U33" si="21">ROUND(S31*$U$1,0)</f>
+        <f t="shared" ref="U31:U33" si="22">ROUND(S31*$U$1,0)</f>
         <v>77</v>
       </c>
       <c r="V31" s="19"/>
@@ -10508,10 +10593,13 @@
         <v>46</v>
       </c>
       <c r="AK31" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>30.8</v>
       </c>
-      <c r="AL31" s="8"/>
+      <c r="AL31" s="8">
+        <f t="shared" si="11"/>
+        <v>8.4</v>
+      </c>
       <c r="AM31" s="8"/>
       <c r="AN31" s="8"/>
       <c r="AO31" s="8"/>
@@ -10580,7 +10668,7 @@
         <v>71.2</v>
       </c>
       <c r="R32" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>201</v>
       </c>
       <c r="S32" s="4">
@@ -10588,11 +10676,11 @@
         <v>240</v>
       </c>
       <c r="T32" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>144</v>
       </c>
       <c r="U32" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>96</v>
       </c>
       <c r="V32" s="19">
@@ -10645,10 +10733,13 @@
         <v>57.6</v>
       </c>
       <c r="AK32" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>38.400000000000006</v>
       </c>
-      <c r="AL32" s="8"/>
+      <c r="AL32" s="8">
+        <f t="shared" si="11"/>
+        <v>28.480000000000004</v>
+      </c>
       <c r="AM32" s="8"/>
       <c r="AN32" s="8"/>
       <c r="AO32" s="8"/>
@@ -10715,7 +10806,7 @@
         <v>136.4</v>
       </c>
       <c r="R33" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>883</v>
       </c>
       <c r="S33" s="4">
@@ -10723,11 +10814,11 @@
         <v>883</v>
       </c>
       <c r="T33" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>530</v>
       </c>
       <c r="U33" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>353</v>
       </c>
       <c r="V33" s="19"/>
@@ -10775,10 +10866,13 @@
         <v>212</v>
       </c>
       <c r="AK33" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>141.20000000000002</v>
       </c>
-      <c r="AL33" s="8"/>
+      <c r="AL33" s="8">
+        <f t="shared" si="11"/>
+        <v>54.56</v>
+      </c>
       <c r="AM33" s="8"/>
       <c r="AN33" s="8"/>
       <c r="AO33" s="8"/>
@@ -10844,7 +10938,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U34" s="4"/>
@@ -10895,10 +10989,13 @@
         <v>0</v>
       </c>
       <c r="AK34" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL34" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL34" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM34" s="8"/>
       <c r="AN34" s="8"/>
       <c r="AO34" s="8"/>
@@ -10962,7 +11059,7 @@
         <v>0</v>
       </c>
       <c r="T35" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U35" s="4"/>
@@ -11011,10 +11108,13 @@
         <v>0</v>
       </c>
       <c r="AK35" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL35" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL35" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM35" s="8"/>
       <c r="AN35" s="8"/>
       <c r="AO35" s="8"/>
@@ -11074,7 +11174,7 @@
         <v>0</v>
       </c>
       <c r="T36" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U36" s="4"/>
@@ -11123,10 +11223,13 @@
         <v>0</v>
       </c>
       <c r="AK36" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL36" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL36" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM36" s="8"/>
       <c r="AN36" s="8"/>
       <c r="AO36" s="8"/>
@@ -11194,7 +11297,7 @@
         <v>0</v>
       </c>
       <c r="T37" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U37" s="4"/>
@@ -11243,10 +11346,13 @@
         <v>0</v>
       </c>
       <c r="AK37" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL37" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL37" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM37" s="8"/>
       <c r="AN37" s="8"/>
       <c r="AO37" s="8"/>
@@ -11294,11 +11400,11 @@
         <v>53</v>
       </c>
       <c r="L38" s="11">
-        <f t="shared" ref="L38:L69" si="22">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="23">E38-K38</f>
         <v>-38</v>
       </c>
       <c r="M38" s="11">
-        <f t="shared" ref="M38:M69" si="23">E38-N38</f>
+        <f t="shared" ref="M38:M69" si="24">E38-N38</f>
         <v>15</v>
       </c>
       <c r="N38" s="11"/>
@@ -11307,7 +11413,7 @@
       </c>
       <c r="P38" s="11"/>
       <c r="Q38" s="11">
-        <f t="shared" ref="Q38:Q69" si="24">M38/5</f>
+        <f t="shared" ref="Q38:Q69" si="25">M38/5</f>
         <v>3</v>
       </c>
       <c r="R38" s="14"/>
@@ -11316,7 +11422,7 @@
         <v>0</v>
       </c>
       <c r="T38" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U38" s="4"/>
@@ -11326,7 +11432,7 @@
         <v>0</v>
       </c>
       <c r="X38" s="11">
-        <f t="shared" ref="X38:X69" si="25">(F38+O38+P38)/Q38</f>
+        <f t="shared" ref="X38:X69" si="26">(F38+O38+P38)/Q38</f>
         <v>0</v>
       </c>
       <c r="Y38" s="11">
@@ -11367,10 +11473,13 @@
         <v>0</v>
       </c>
       <c r="AK38" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL38" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL38" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM38" s="8"/>
       <c r="AN38" s="8"/>
       <c r="AO38" s="8"/>
@@ -11418,11 +11527,11 @@
         <v>133.61500000000001</v>
       </c>
       <c r="L39" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-0.44700000000000273</v>
       </c>
       <c r="M39" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>92.853000000000009</v>
       </c>
       <c r="N39" s="8">
@@ -11433,11 +11542,11 @@
       </c>
       <c r="P39" s="8"/>
       <c r="Q39" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>18.570600000000002</v>
       </c>
       <c r="R39" s="4">
-        <f t="shared" ref="R39:R40" si="26">15*Q39-P39-O39-F39</f>
+        <f t="shared" ref="R39:R40" si="27">15*Q39-P39-O39-F39</f>
         <v>44.03400000000002</v>
       </c>
       <c r="S39" s="4">
@@ -11445,7 +11554,7 @@
         <v>70</v>
       </c>
       <c r="T39" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>70</v>
       </c>
       <c r="U39" s="4"/>
@@ -11458,7 +11567,7 @@
         <v>16.398231613410442</v>
       </c>
       <c r="X39" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>12.62883267099609</v>
       </c>
       <c r="Y39" s="8">
@@ -11497,10 +11606,13 @@
         <v>70</v>
       </c>
       <c r="AK39" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL39" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL39" s="8">
+        <f t="shared" si="11"/>
+        <v>18.570600000000002</v>
+      </c>
       <c r="AM39" s="8"/>
       <c r="AN39" s="8"/>
       <c r="AO39" s="8"/>
@@ -11548,11 +11660,11 @@
         <v>39.1</v>
       </c>
       <c r="L40" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-2.4570000000000007</v>
       </c>
       <c r="M40" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>36.643000000000001</v>
       </c>
       <c r="N40" s="8"/>
@@ -11561,11 +11673,11 @@
       </c>
       <c r="P40" s="8"/>
       <c r="Q40" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>7.3285999999999998</v>
       </c>
       <c r="R40" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>8.0400000000000027</v>
       </c>
       <c r="S40" s="4">
@@ -11573,7 +11685,7 @@
         <v>8</v>
       </c>
       <c r="T40" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8</v>
       </c>
       <c r="U40" s="4"/>
@@ -11583,7 +11695,7 @@
         <v>14.994541931610403</v>
       </c>
       <c r="X40" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>13.902928253691019</v>
       </c>
       <c r="Y40" s="8">
@@ -11622,10 +11734,13 @@
         <v>8</v>
       </c>
       <c r="AK40" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL40" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL40" s="8">
+        <f t="shared" si="11"/>
+        <v>7.3285999999999998</v>
+      </c>
       <c r="AM40" s="8"/>
       <c r="AN40" s="8"/>
       <c r="AO40" s="8"/>
@@ -11673,11 +11788,11 @@
         <v>154.24</v>
       </c>
       <c r="L41" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-27.428000000000011</v>
       </c>
       <c r="M41" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>107.97199999999999</v>
       </c>
       <c r="N41" s="8">
@@ -11688,7 +11803,7 @@
       </c>
       <c r="P41" s="8"/>
       <c r="Q41" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>21.5944</v>
       </c>
       <c r="R41" s="4">
@@ -11700,7 +11815,7 @@
         <v>174</v>
       </c>
       <c r="T41" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>104</v>
       </c>
       <c r="U41" s="4">
@@ -11713,7 +11828,7 @@
         <v>10.984375578853776</v>
       </c>
       <c r="X41" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>2.926731004334457</v>
       </c>
       <c r="Y41" s="8">
@@ -11752,10 +11867,13 @@
         <v>104</v>
       </c>
       <c r="AK41" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>70</v>
       </c>
-      <c r="AL41" s="8"/>
+      <c r="AL41" s="8">
+        <f t="shared" si="11"/>
+        <v>21.5944</v>
+      </c>
       <c r="AM41" s="8"/>
       <c r="AN41" s="8"/>
       <c r="AO41" s="8"/>
@@ -11801,11 +11919,11 @@
         <v>73</v>
       </c>
       <c r="L42" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-63</v>
       </c>
       <c r="M42" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="N42" s="11"/>
@@ -11814,7 +11932,7 @@
       </c>
       <c r="P42" s="11"/>
       <c r="Q42" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2</v>
       </c>
       <c r="R42" s="14"/>
@@ -11823,7 +11941,7 @@
         <v>0</v>
       </c>
       <c r="T42" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U42" s="4"/>
@@ -11833,7 +11951,7 @@
         <v>222.5</v>
       </c>
       <c r="X42" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>222.5</v>
       </c>
       <c r="Y42" s="11">
@@ -11874,10 +11992,13 @@
         <v>0</v>
       </c>
       <c r="AK42" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL42" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL42" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM42" s="8"/>
       <c r="AN42" s="8"/>
       <c r="AO42" s="8"/>
@@ -11925,11 +12046,11 @@
         <v>146.19999999999999</v>
       </c>
       <c r="L43" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-10.972999999999985</v>
       </c>
       <c r="M43" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>135.227</v>
       </c>
       <c r="N43" s="8"/>
@@ -11938,7 +12059,7 @@
       </c>
       <c r="P43" s="8"/>
       <c r="Q43" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>27.045400000000001</v>
       </c>
       <c r="R43" s="4">
@@ -11950,11 +12071,11 @@
         <v>237</v>
       </c>
       <c r="T43" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>142</v>
       </c>
       <c r="U43" s="4">
-        <f t="shared" ref="U43:U44" si="27">ROUND(S43*$U$1,0)</f>
+        <f t="shared" ref="U43:U44" si="28">ROUND(S43*$U$1,0)</f>
         <v>95</v>
       </c>
       <c r="V43" s="19"/>
@@ -11963,7 +12084,7 @@
         <v>14.015248434114488</v>
       </c>
       <c r="X43" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>5.2522055506666563</v>
       </c>
       <c r="Y43" s="8">
@@ -12002,10 +12123,13 @@
         <v>142</v>
       </c>
       <c r="AK43" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>95</v>
       </c>
-      <c r="AL43" s="8"/>
+      <c r="AL43" s="8">
+        <f t="shared" si="11"/>
+        <v>27.045400000000001</v>
+      </c>
       <c r="AM43" s="8"/>
       <c r="AN43" s="8"/>
       <c r="AO43" s="8"/>
@@ -12053,11 +12177,11 @@
         <v>602</v>
       </c>
       <c r="L44" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-169</v>
       </c>
       <c r="M44" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>401</v>
       </c>
       <c r="N44" s="8">
@@ -12070,11 +12194,11 @@
         <v>264</v>
       </c>
       <c r="Q44" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>80.2</v>
       </c>
       <c r="R44" s="4">
-        <f t="shared" ref="R44:R47" si="28">15*Q44-P44-O44-F44</f>
+        <f t="shared" ref="R44:R47" si="29">15*Q44-P44-O44-F44</f>
         <v>618</v>
       </c>
       <c r="S44" s="4">
@@ -12082,11 +12206,11 @@
         <v>618</v>
       </c>
       <c r="T44" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>371</v>
       </c>
       <c r="U44" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>247</v>
       </c>
       <c r="V44" s="19"/>
@@ -12095,7 +12219,7 @@
         <v>15</v>
       </c>
       <c r="X44" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>7.2942643391521198</v>
       </c>
       <c r="Y44" s="8">
@@ -12136,10 +12260,13 @@
         <v>111.3</v>
       </c>
       <c r="AK44" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="AL44" s="8"/>
+      <c r="AL44" s="8">
+        <f t="shared" si="11"/>
+        <v>24.06</v>
+      </c>
       <c r="AM44" s="8"/>
       <c r="AN44" s="8"/>
       <c r="AO44" s="8"/>
@@ -12187,11 +12314,11 @@
         <v>19.725999999999999</v>
       </c>
       <c r="L45" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2.1039999999999992</v>
       </c>
       <c r="M45" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>21.83</v>
       </c>
       <c r="N45" s="8"/>
@@ -12200,7 +12327,7 @@
       </c>
       <c r="P45" s="8"/>
       <c r="Q45" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>4.3659999999999997</v>
       </c>
       <c r="R45" s="4"/>
@@ -12209,7 +12336,7 @@
         <v>0</v>
       </c>
       <c r="T45" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U45" s="4"/>
@@ -12219,7 +12346,7 @@
         <v>20.728355474118189</v>
       </c>
       <c r="X45" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>20.728355474118189</v>
       </c>
       <c r="Y45" s="8">
@@ -12260,10 +12387,13 @@
         <v>0</v>
       </c>
       <c r="AK45" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL45" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL45" s="8">
+        <f t="shared" si="11"/>
+        <v>4.3659999999999997</v>
+      </c>
       <c r="AM45" s="8"/>
       <c r="AN45" s="8"/>
       <c r="AO45" s="8"/>
@@ -12311,11 +12441,11 @@
         <v>4.5</v>
       </c>
       <c r="L46" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-1.4319999999999999</v>
       </c>
       <c r="M46" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>3.0680000000000001</v>
       </c>
       <c r="N46" s="8"/>
@@ -12324,7 +12454,7 @@
       </c>
       <c r="P46" s="8"/>
       <c r="Q46" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.61360000000000003</v>
       </c>
       <c r="R46" s="4">
@@ -12335,7 +12465,7 @@
         <v>4</v>
       </c>
       <c r="T46" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="U46" s="4"/>
@@ -12345,7 +12475,7 @@
         <v>18.994458930899608</v>
       </c>
       <c r="X46" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>12.475554106910039</v>
       </c>
       <c r="Y46" s="8">
@@ -12384,10 +12514,13 @@
         <v>4</v>
       </c>
       <c r="AK46" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL46" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL46" s="8">
+        <f t="shared" si="11"/>
+        <v>0.61360000000000003</v>
+      </c>
       <c r="AM46" s="8"/>
       <c r="AN46" s="8"/>
       <c r="AO46" s="8"/>
@@ -12435,11 +12568,11 @@
         <v>1466</v>
       </c>
       <c r="L47" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-491</v>
       </c>
       <c r="M47" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>919</v>
       </c>
       <c r="N47" s="8">
@@ -12452,11 +12585,11 @@
         <v>715</v>
       </c>
       <c r="Q47" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>183.8</v>
       </c>
       <c r="R47" s="4">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>474</v>
       </c>
       <c r="S47" s="4">
@@ -12464,7 +12597,7 @@
         <v>474</v>
       </c>
       <c r="T47" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>284</v>
       </c>
       <c r="U47" s="4">
@@ -12477,7 +12610,7 @@
         <v>14.999999999999998</v>
       </c>
       <c r="X47" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>12.421109902067464</v>
       </c>
       <c r="Y47" s="8">
@@ -12516,10 +12649,13 @@
         <v>99.399999999999991</v>
       </c>
       <c r="AK47" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>66.5</v>
       </c>
-      <c r="AL47" s="8"/>
+      <c r="AL47" s="8">
+        <f t="shared" si="11"/>
+        <v>64.33</v>
+      </c>
       <c r="AM47" s="8"/>
       <c r="AN47" s="8"/>
       <c r="AO47" s="8"/>
@@ -12569,11 +12705,11 @@
         <v>274</v>
       </c>
       <c r="L48" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-252</v>
       </c>
       <c r="M48" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>22</v>
       </c>
       <c r="N48" s="11"/>
@@ -12582,7 +12718,7 @@
       </c>
       <c r="P48" s="11"/>
       <c r="Q48" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="R48" s="14"/>
@@ -12591,7 +12727,7 @@
         <v>0</v>
       </c>
       <c r="T48" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U48" s="4"/>
@@ -12601,7 +12737,7 @@
         <v>-0.22727272727272727</v>
       </c>
       <c r="X48" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>-0.22727272727272727</v>
       </c>
       <c r="Y48" s="11">
@@ -12642,10 +12778,13 @@
         <v>0</v>
       </c>
       <c r="AK48" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL48" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL48" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM48" s="8"/>
       <c r="AN48" s="8"/>
       <c r="AO48" s="8"/>
@@ -12693,11 +12832,11 @@
         <v>65</v>
       </c>
       <c r="L49" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-1</v>
       </c>
       <c r="M49" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>64</v>
       </c>
       <c r="N49" s="8"/>
@@ -12708,7 +12847,7 @@
         <v>92</v>
       </c>
       <c r="Q49" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>12.8</v>
       </c>
       <c r="R49" s="4">
@@ -12720,7 +12859,7 @@
         <v>17</v>
       </c>
       <c r="T49" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>17</v>
       </c>
       <c r="U49" s="4"/>
@@ -12730,7 +12869,7 @@
         <v>15</v>
       </c>
       <c r="X49" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>13.671875</v>
       </c>
       <c r="Y49" s="8">
@@ -12769,10 +12908,13 @@
         <v>6.97</v>
       </c>
       <c r="AK49" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL49" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL49" s="8">
+        <f t="shared" si="11"/>
+        <v>5.2480000000000002</v>
+      </c>
       <c r="AM49" s="8"/>
       <c r="AN49" s="8"/>
       <c r="AO49" s="8"/>
@@ -12816,11 +12958,11 @@
         <v>30.256</v>
       </c>
       <c r="L50" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M50" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>30.256</v>
       </c>
       <c r="N50" s="11"/>
@@ -12829,7 +12971,7 @@
       </c>
       <c r="P50" s="11"/>
       <c r="Q50" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>6.0511999999999997</v>
       </c>
       <c r="R50" s="14"/>
@@ -12838,7 +12980,7 @@
         <v>0</v>
       </c>
       <c r="T50" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U50" s="4"/>
@@ -12848,7 +12990,7 @@
         <v>6.9105301427815977</v>
       </c>
       <c r="X50" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>6.9105301427815977</v>
       </c>
       <c r="Y50" s="11">
@@ -12887,10 +13029,13 @@
         <v>0</v>
       </c>
       <c r="AK50" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL50" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL50" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM50" s="8"/>
       <c r="AN50" s="8"/>
       <c r="AO50" s="8"/>
@@ -12936,11 +13081,11 @@
         <v>448</v>
       </c>
       <c r="L51" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-319</v>
       </c>
       <c r="M51" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>87</v>
       </c>
       <c r="N51" s="8">
@@ -12953,11 +13098,11 @@
         <v>125</v>
       </c>
       <c r="Q51" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>17.399999999999999</v>
       </c>
       <c r="R51" s="4">
-        <f t="shared" ref="R51:R56" si="29">15*Q51-P51-O51-F51</f>
+        <f t="shared" ref="R51:R56" si="30">15*Q51-P51-O51-F51</f>
         <v>33</v>
       </c>
       <c r="S51" s="4">
@@ -12965,7 +13110,7 @@
         <v>70</v>
       </c>
       <c r="T51" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>70</v>
       </c>
       <c r="U51" s="4"/>
@@ -12978,7 +13123,7 @@
         <v>17.126436781609197</v>
       </c>
       <c r="X51" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>13.103448275862069</v>
       </c>
       <c r="Y51" s="8">
@@ -13017,10 +13162,13 @@
         <v>25.2</v>
       </c>
       <c r="AK51" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL51" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL51" s="8">
+        <f t="shared" si="11"/>
+        <v>6.2639999999999993</v>
+      </c>
       <c r="AM51" s="8"/>
       <c r="AN51" s="8"/>
       <c r="AO51" s="8"/>
@@ -13068,11 +13216,11 @@
         <v>411</v>
       </c>
       <c r="L52" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-300</v>
       </c>
       <c r="M52" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>111</v>
       </c>
       <c r="N52" s="8"/>
@@ -13083,7 +13231,7 @@
         <v>261</v>
       </c>
       <c r="Q52" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>22.2</v>
       </c>
       <c r="R52" s="4">
@@ -13094,7 +13242,7 @@
         <v>100</v>
       </c>
       <c r="T52" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>100</v>
       </c>
       <c r="U52" s="4"/>
@@ -13104,7 +13252,7 @@
         <v>33.288288288288292</v>
       </c>
       <c r="X52" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>28.783783783783786</v>
       </c>
       <c r="Y52" s="8">
@@ -13145,10 +13293,13 @@
         <v>33</v>
       </c>
       <c r="AK52" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL52" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL52" s="8">
+        <f t="shared" si="11"/>
+        <v>7.3260000000000005</v>
+      </c>
       <c r="AM52" s="8"/>
       <c r="AN52" s="8"/>
       <c r="AO52" s="8"/>
@@ -13196,11 +13347,11 @@
         <v>468</v>
       </c>
       <c r="L53" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-388</v>
       </c>
       <c r="M53" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>56</v>
       </c>
       <c r="N53" s="8">
@@ -13213,7 +13364,7 @@
         <v>83</v>
       </c>
       <c r="Q53" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>11.2</v>
       </c>
       <c r="R53" s="4">
@@ -13224,7 +13375,7 @@
         <v>300</v>
       </c>
       <c r="T53" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>180</v>
       </c>
       <c r="U53" s="4">
@@ -13237,7 +13388,7 @@
         <v>44.464285714285715</v>
       </c>
       <c r="X53" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>17.678571428571431</v>
       </c>
       <c r="Y53" s="8">
@@ -13278,10 +13429,13 @@
         <v>72</v>
       </c>
       <c r="AK53" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>48</v>
       </c>
-      <c r="AL53" s="8"/>
+      <c r="AL53" s="8">
+        <f t="shared" si="11"/>
+        <v>4.4799999999999995</v>
+      </c>
       <c r="AM53" s="8"/>
       <c r="AN53" s="8"/>
       <c r="AO53" s="8"/>
@@ -13329,11 +13483,11 @@
         <v>20</v>
       </c>
       <c r="L54" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-10</v>
       </c>
       <c r="M54" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
       <c r="N54" s="8"/>
@@ -13342,7 +13496,7 @@
       </c>
       <c r="P54" s="8"/>
       <c r="Q54" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2</v>
       </c>
       <c r="R54" s="4"/>
@@ -13351,7 +13505,7 @@
         <v>0</v>
       </c>
       <c r="T54" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U54" s="4"/>
@@ -13361,7 +13515,7 @@
         <v>15.5</v>
       </c>
       <c r="X54" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>15.5</v>
       </c>
       <c r="Y54" s="8">
@@ -13400,10 +13554,13 @@
         <v>0</v>
       </c>
       <c r="AK54" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL54" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL54" s="8">
+        <f t="shared" si="11"/>
+        <v>0.66</v>
+      </c>
       <c r="AM54" s="8"/>
       <c r="AN54" s="8"/>
       <c r="AO54" s="8"/>
@@ -13451,11 +13608,11 @@
         <v>371.029</v>
       </c>
       <c r="L55" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>9.6190000000000282</v>
       </c>
       <c r="M55" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>340.01900000000001</v>
       </c>
       <c r="N55" s="8">
@@ -13466,11 +13623,11 @@
       </c>
       <c r="P55" s="8"/>
       <c r="Q55" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>68.003799999999998</v>
       </c>
       <c r="R55" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>408.67399999999998</v>
       </c>
       <c r="S55" s="4">
@@ -13478,7 +13635,7 @@
         <v>409</v>
       </c>
       <c r="T55" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>245</v>
       </c>
       <c r="U55" s="4">
@@ -13491,7 +13648,7 @@
         <v>15.004793849755456</v>
       </c>
       <c r="X55" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>8.9904240645375708</v>
       </c>
       <c r="Y55" s="8">
@@ -13530,10 +13687,13 @@
         <v>245</v>
       </c>
       <c r="AK55" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>164</v>
       </c>
-      <c r="AL55" s="8"/>
+      <c r="AL55" s="8">
+        <f t="shared" si="11"/>
+        <v>68.003799999999998</v>
+      </c>
       <c r="AM55" s="8"/>
       <c r="AN55" s="8"/>
       <c r="AO55" s="8"/>
@@ -13581,11 +13741,11 @@
         <v>53</v>
       </c>
       <c r="L56" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-11</v>
       </c>
       <c r="M56" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>42</v>
       </c>
       <c r="N56" s="8"/>
@@ -13594,11 +13754,11 @@
       </c>
       <c r="P56" s="8"/>
       <c r="Q56" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>8.4</v>
       </c>
       <c r="R56" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>40</v>
       </c>
       <c r="S56" s="4">
@@ -13606,7 +13766,7 @@
         <v>40</v>
       </c>
       <c r="T56" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>40</v>
       </c>
       <c r="U56" s="4"/>
@@ -13616,7 +13776,7 @@
         <v>15</v>
       </c>
       <c r="X56" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>10.238095238095237</v>
       </c>
       <c r="Y56" s="8">
@@ -13655,10 +13815,13 @@
         <v>16</v>
       </c>
       <c r="AK56" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL56" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL56" s="8">
+        <f t="shared" si="11"/>
+        <v>3.3600000000000003</v>
+      </c>
       <c r="AM56" s="8"/>
       <c r="AN56" s="8"/>
       <c r="AO56" s="8"/>
@@ -13708,11 +13871,11 @@
         <v>14</v>
       </c>
       <c r="L57" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-8.3999999999999631E-2</v>
       </c>
       <c r="M57" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>13.916</v>
       </c>
       <c r="N57" s="11"/>
@@ -13721,7 +13884,7 @@
       </c>
       <c r="P57" s="11"/>
       <c r="Q57" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2.7831999999999999</v>
       </c>
       <c r="R57" s="14"/>
@@ -13730,7 +13893,7 @@
         <v>0</v>
       </c>
       <c r="T57" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U57" s="4"/>
@@ -13740,7 +13903,7 @@
         <v>11.463064098878988</v>
       </c>
       <c r="X57" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>11.463064098878988</v>
       </c>
       <c r="Y57" s="11">
@@ -13781,10 +13944,13 @@
         <v>0</v>
       </c>
       <c r="AK57" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL57" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL57" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM57" s="8"/>
       <c r="AN57" s="8"/>
       <c r="AO57" s="8"/>
@@ -13830,11 +13996,11 @@
         <v>19.399999999999999</v>
       </c>
       <c r="L58" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-5.3179999999999978</v>
       </c>
       <c r="M58" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>14.082000000000001</v>
       </c>
       <c r="N58" s="8"/>
@@ -13843,7 +14009,7 @@
       </c>
       <c r="P58" s="8"/>
       <c r="Q58" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2.8164000000000002</v>
       </c>
       <c r="R58" s="4">
@@ -13854,7 +14020,7 @@
         <v>4</v>
       </c>
       <c r="T58" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="U58" s="4"/>
@@ -13864,7 +14030,7 @@
         <v>15.977844056242009</v>
       </c>
       <c r="X58" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>14.557591251242719</v>
       </c>
       <c r="Y58" s="8">
@@ -13903,10 +14069,13 @@
         <v>4</v>
       </c>
       <c r="AK58" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL58" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL58" s="8">
+        <f t="shared" si="11"/>
+        <v>2.8164000000000002</v>
+      </c>
       <c r="AM58" s="8"/>
       <c r="AN58" s="8"/>
       <c r="AO58" s="8"/>
@@ -13954,11 +14123,11 @@
         <v>5.5460000000000003</v>
       </c>
       <c r="L59" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-3.6999999999999922E-2</v>
       </c>
       <c r="M59" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>5.5090000000000003</v>
       </c>
       <c r="N59" s="8"/>
@@ -13967,7 +14136,7 @@
       </c>
       <c r="P59" s="8"/>
       <c r="Q59" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1.1018000000000001</v>
       </c>
       <c r="R59" s="4"/>
@@ -13976,7 +14145,7 @@
         <v>0</v>
       </c>
       <c r="T59" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U59" s="4"/>
@@ -13986,7 +14155,7 @@
         <v>17.705572699219456</v>
       </c>
       <c r="X59" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>17.705572699219456</v>
       </c>
       <c r="Y59" s="8">
@@ -14027,10 +14196,13 @@
         <v>0</v>
       </c>
       <c r="AK59" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL59" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL59" s="8">
+        <f t="shared" si="11"/>
+        <v>1.1018000000000001</v>
+      </c>
       <c r="AM59" s="8"/>
       <c r="AN59" s="8"/>
       <c r="AO59" s="8"/>
@@ -14072,11 +14244,11 @@
         <v>80</v>
       </c>
       <c r="L60" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M60" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N60" s="11">
@@ -14085,7 +14257,7 @@
       <c r="O60" s="11"/>
       <c r="P60" s="11"/>
       <c r="Q60" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="R60" s="14"/>
@@ -14094,7 +14266,7 @@
         <v>0</v>
       </c>
       <c r="T60" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U60" s="4"/>
@@ -14104,7 +14276,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="X60" s="11" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y60" s="11">
@@ -14143,10 +14315,13 @@
         <v>0</v>
       </c>
       <c r="AK60" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL60" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL60" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM60" s="8"/>
       <c r="AN60" s="8"/>
       <c r="AO60" s="8"/>
@@ -14192,11 +14367,11 @@
         <v>158</v>
       </c>
       <c r="L61" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-109</v>
       </c>
       <c r="M61" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>33</v>
       </c>
       <c r="N61" s="8">
@@ -14209,7 +14384,7 @@
         <v>72</v>
       </c>
       <c r="Q61" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>6.6</v>
       </c>
       <c r="R61" s="4">
@@ -14220,7 +14395,7 @@
         <v>50</v>
       </c>
       <c r="T61" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>50</v>
       </c>
       <c r="U61" s="4"/>
@@ -14230,7 +14405,7 @@
         <v>27.272727272727273</v>
       </c>
       <c r="X61" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>19.696969696969699</v>
       </c>
       <c r="Y61" s="8">
@@ -14269,10 +14444,13 @@
         <v>12.5</v>
       </c>
       <c r="AK61" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL61" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL61" s="8">
+        <f t="shared" si="11"/>
+        <v>1.65</v>
+      </c>
       <c r="AM61" s="8"/>
       <c r="AN61" s="8"/>
       <c r="AO61" s="8"/>
@@ -14320,11 +14498,11 @@
         <v>19.326000000000001</v>
       </c>
       <c r="L62" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-0.90800000000000125</v>
       </c>
       <c r="M62" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>18.417999999999999</v>
       </c>
       <c r="N62" s="8"/>
@@ -14333,11 +14511,11 @@
       </c>
       <c r="P62" s="8"/>
       <c r="Q62" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>3.6835999999999998</v>
       </c>
       <c r="R62" s="4">
-        <f t="shared" ref="R62:R67" si="30">15*Q62-P62-O62-F62</f>
+        <f t="shared" ref="R62:R67" si="31">15*Q62-P62-O62-F62</f>
         <v>25.217999999999996</v>
       </c>
       <c r="S62" s="4">
@@ -14345,7 +14523,7 @@
         <v>25</v>
       </c>
       <c r="T62" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>25</v>
       </c>
       <c r="U62" s="4"/>
@@ -14355,7 +14533,7 @@
         <v>14.940818764252363</v>
       </c>
       <c r="X62" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>8.1539798023672496</v>
       </c>
       <c r="Y62" s="8">
@@ -14394,10 +14572,13 @@
         <v>25</v>
       </c>
       <c r="AK62" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL62" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL62" s="8">
+        <f t="shared" si="11"/>
+        <v>3.6835999999999998</v>
+      </c>
       <c r="AM62" s="8"/>
       <c r="AN62" s="8"/>
       <c r="AO62" s="8"/>
@@ -14441,11 +14622,11 @@
         <v>51</v>
       </c>
       <c r="L63" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-4</v>
       </c>
       <c r="M63" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>15</v>
       </c>
       <c r="N63" s="8">
@@ -14456,7 +14637,7 @@
       </c>
       <c r="P63" s="8"/>
       <c r="Q63" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>3</v>
       </c>
       <c r="R63" s="4">
@@ -14468,7 +14649,7 @@
         <v>28</v>
       </c>
       <c r="T63" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>28</v>
       </c>
       <c r="U63" s="4"/>
@@ -14478,7 +14659,7 @@
         <v>12</v>
       </c>
       <c r="X63" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>2.6666666666666665</v>
       </c>
       <c r="Y63" s="8">
@@ -14519,10 +14700,13 @@
         <v>7.5600000000000005</v>
       </c>
       <c r="AK63" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL63" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL63" s="8">
+        <f t="shared" si="11"/>
+        <v>0.81</v>
+      </c>
       <c r="AM63" s="8"/>
       <c r="AN63" s="8"/>
       <c r="AO63" s="8"/>
@@ -14570,11 +14754,11 @@
         <v>157</v>
       </c>
       <c r="L64" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-25</v>
       </c>
       <c r="M64" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>100</v>
       </c>
       <c r="N64" s="8">
@@ -14587,11 +14771,11 @@
         <v>83</v>
       </c>
       <c r="Q64" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="R64" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>143</v>
       </c>
       <c r="S64" s="4">
@@ -14599,11 +14783,11 @@
         <v>143</v>
       </c>
       <c r="T64" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>86</v>
       </c>
       <c r="U64" s="4">
-        <f t="shared" ref="U64:U66" si="31">ROUND(S64*$U$1,0)</f>
+        <f t="shared" ref="U64:U66" si="32">ROUND(S64*$U$1,0)</f>
         <v>57</v>
       </c>
       <c r="V64" s="19"/>
@@ -14612,7 +14796,7 @@
         <v>15</v>
       </c>
       <c r="X64" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>7.85</v>
       </c>
       <c r="Y64" s="8">
@@ -14651,10 +14835,13 @@
         <v>25.8</v>
       </c>
       <c r="AK64" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>17.099999999999998</v>
       </c>
-      <c r="AL64" s="8"/>
+      <c r="AL64" s="8">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
       <c r="AM64" s="8"/>
       <c r="AN64" s="8"/>
       <c r="AO64" s="8"/>
@@ -14702,11 +14889,11 @@
         <v>1947</v>
       </c>
       <c r="L65" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-425</v>
       </c>
       <c r="M65" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1442</v>
       </c>
       <c r="N65" s="8">
@@ -14719,11 +14906,11 @@
         <v>919</v>
       </c>
       <c r="Q65" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>288.39999999999998</v>
       </c>
       <c r="R65" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1857</v>
       </c>
       <c r="S65" s="4">
@@ -14731,11 +14918,11 @@
         <v>1857</v>
       </c>
       <c r="T65" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1114</v>
       </c>
       <c r="U65" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>743</v>
       </c>
       <c r="V65" s="19"/>
@@ -14744,7 +14931,7 @@
         <v>15.000000000000002</v>
       </c>
       <c r="X65" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>8.5610263522884882</v>
       </c>
       <c r="Y65" s="8">
@@ -14785,10 +14972,13 @@
         <v>456.73999999999995</v>
       </c>
       <c r="AK65" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>304.63</v>
       </c>
-      <c r="AL65" s="8"/>
+      <c r="AL65" s="8">
+        <f t="shared" si="11"/>
+        <v>118.24399999999999</v>
+      </c>
       <c r="AM65" s="8"/>
       <c r="AN65" s="8"/>
       <c r="AO65" s="8"/>
@@ -14836,11 +15026,11 @@
         <v>518.02</v>
       </c>
       <c r="L66" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-3.1620000000000346</v>
       </c>
       <c r="M66" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>415.93799999999993</v>
       </c>
       <c r="N66" s="8">
@@ -14851,22 +15041,22 @@
       </c>
       <c r="P66" s="8"/>
       <c r="Q66" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>83.187599999999989</v>
       </c>
       <c r="R66" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>741.52699999999982</v>
       </c>
       <c r="S66" s="4">
         <v>1350</v>
       </c>
       <c r="T66" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>810</v>
       </c>
       <c r="U66" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>540</v>
       </c>
       <c r="V66" s="19" t="str">
@@ -14878,7 +15068,7 @@
         <v>22.314467540835416</v>
       </c>
       <c r="X66" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>6.0860873495569052</v>
       </c>
       <c r="Y66" s="8">
@@ -14919,10 +15109,13 @@
         <v>810</v>
       </c>
       <c r="AK66" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>540</v>
       </c>
-      <c r="AL66" s="8"/>
+      <c r="AL66" s="8">
+        <f t="shared" si="11"/>
+        <v>83.187599999999989</v>
+      </c>
       <c r="AM66" s="8"/>
       <c r="AN66" s="8"/>
       <c r="AO66" s="8"/>
@@ -14970,11 +15163,11 @@
         <v>61</v>
       </c>
       <c r="L67" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-2</v>
       </c>
       <c r="M67" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>59</v>
       </c>
       <c r="N67" s="8"/>
@@ -14983,11 +15176,11 @@
       </c>
       <c r="P67" s="8"/>
       <c r="Q67" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>11.8</v>
       </c>
       <c r="R67" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>49</v>
       </c>
       <c r="S67" s="4">
@@ -14995,7 +15188,7 @@
         <v>49</v>
       </c>
       <c r="T67" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>49</v>
       </c>
       <c r="U67" s="4"/>
@@ -15005,7 +15198,7 @@
         <v>14.999999999999998</v>
       </c>
       <c r="X67" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>10.847457627118644</v>
       </c>
       <c r="Y67" s="8">
@@ -15044,10 +15237,13 @@
         <v>17.149999999999999</v>
       </c>
       <c r="AK67" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL67" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL67" s="8">
+        <f t="shared" si="11"/>
+        <v>4.13</v>
+      </c>
       <c r="AM67" s="8"/>
       <c r="AN67" s="8"/>
       <c r="AO67" s="8"/>
@@ -15085,11 +15281,11 @@
         <v>5.8</v>
       </c>
       <c r="L68" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-5.8</v>
       </c>
       <c r="M68" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N68" s="11"/>
@@ -15098,7 +15294,7 @@
       </c>
       <c r="P68" s="11"/>
       <c r="Q68" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="R68" s="14"/>
@@ -15107,7 +15303,7 @@
         <v>0</v>
       </c>
       <c r="T68" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U68" s="4"/>
@@ -15117,7 +15313,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="X68" s="11" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y68" s="11">
@@ -15158,10 +15354,13 @@
         <v>0</v>
       </c>
       <c r="AK68" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AL68" s="8"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL68" s="8">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AM68" s="8"/>
       <c r="AN68" s="8"/>
       <c r="AO68" s="8"/>
@@ -15209,11 +15408,11 @@
         <v>943</v>
       </c>
       <c r="L69" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-243</v>
       </c>
       <c r="M69" s="8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>700</v>
       </c>
       <c r="N69" s="8"/>
@@ -15224,11 +15423,11 @@
         <v>220</v>
       </c>
       <c r="Q69" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>140</v>
       </c>
       <c r="R69" s="4">
-        <f t="shared" ref="R69:R71" si="32">15*Q69-P69-O69-F69</f>
+        <f t="shared" ref="R69:R71" si="33">15*Q69-P69-O69-F69</f>
         <v>1086</v>
       </c>
       <c r="S69" s="4">
@@ -15236,11 +15435,11 @@
         <v>1086</v>
       </c>
       <c r="T69" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>652</v>
       </c>
       <c r="U69" s="4">
-        <f t="shared" ref="U69:U70" si="33">ROUND(S69*$U$1,0)</f>
+        <f t="shared" ref="U69:U70" si="34">ROUND(S69*$U$1,0)</f>
         <v>434</v>
       </c>
       <c r="V69" s="19"/>
@@ -15249,7 +15448,7 @@
         <v>15</v>
       </c>
       <c r="X69" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>7.2428571428571429</v>
       </c>
       <c r="Y69" s="8">
@@ -15288,10 +15487,13 @@
         <v>267.32</v>
       </c>
       <c r="AK69" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>177.94</v>
       </c>
-      <c r="AL69" s="8"/>
+      <c r="AL69" s="8">
+        <f t="shared" si="11"/>
+        <v>57.4</v>
+      </c>
       <c r="AM69" s="8"/>
       <c r="AN69" s="8"/>
       <c r="AO69" s="8"/>
@@ -15339,11 +15541,11 @@
         <v>87.6</v>
       </c>
       <c r="L70" s="8">
-        <f t="shared" ref="L70:L101" si="34">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="35">E70-K70</f>
         <v>-4.6569999999999965</v>
       </c>
       <c r="M70" s="8">
-        <f t="shared" ref="M70:M101" si="35">E70-N70</f>
+        <f t="shared" ref="M70:M101" si="36">E70-N70</f>
         <v>82.942999999999998</v>
       </c>
       <c r="N70" s="8"/>
@@ -15352,7 +15554,7 @@
       </c>
       <c r="P70" s="8"/>
       <c r="Q70" s="8">
-        <f t="shared" ref="Q70:Q101" si="36">M70/5</f>
+        <f t="shared" ref="Q70:Q101" si="37">M70/5</f>
         <v>16.5886</v>
       </c>
       <c r="R70" s="4">
@@ -15364,11 +15566,11 @@
         <v>141</v>
       </c>
       <c r="T70" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>85</v>
       </c>
       <c r="U70" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>56</v>
       </c>
       <c r="V70" s="19"/>
@@ -15377,7 +15579,7 @@
         <v>10.012840143230893</v>
       </c>
       <c r="X70" s="8">
-        <f t="shared" ref="X70:X101" si="37">(F70+O70+P70)/Q70</f>
+        <f t="shared" ref="X70:X101" si="38">(F70+O70+P70)/Q70</f>
         <v>1.5130270185549113</v>
       </c>
       <c r="Y70" s="8">
@@ -15416,10 +15618,13 @@
         <v>85</v>
       </c>
       <c r="AK70" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>56</v>
       </c>
-      <c r="AL70" s="8"/>
+      <c r="AL70" s="8">
+        <f t="shared" si="11"/>
+        <v>16.5886</v>
+      </c>
       <c r="AM70" s="8"/>
       <c r="AN70" s="8"/>
       <c r="AO70" s="8"/>
@@ -15467,11 +15672,11 @@
         <v>241</v>
       </c>
       <c r="L71" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-144</v>
       </c>
       <c r="M71" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>79</v>
       </c>
       <c r="N71" s="8">
@@ -15484,29 +15689,29 @@
         <v>61</v>
       </c>
       <c r="Q71" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>15.8</v>
       </c>
       <c r="R71" s="4">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>84</v>
       </c>
       <c r="S71" s="4">
-        <f t="shared" ref="S71:S123" si="38">ROUND(R71,0)</f>
+        <f t="shared" ref="S71:S123" si="39">ROUND(R71,0)</f>
         <v>84</v>
       </c>
       <c r="T71" s="4">
-        <f t="shared" ref="T71:T123" si="39">ROUND(S71-U71,0)</f>
+        <f t="shared" ref="T71:T123" si="40">ROUND(S71-U71,0)</f>
         <v>84</v>
       </c>
       <c r="U71" s="4"/>
       <c r="V71" s="19"/>
       <c r="W71" s="8">
-        <f t="shared" ref="W71:W123" si="40">(F71+O71+P71+S71)/Q71</f>
+        <f t="shared" ref="W71:W123" si="41">(F71+O71+P71+S71)/Q71</f>
         <v>15</v>
       </c>
       <c r="X71" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>9.6835443037974684</v>
       </c>
       <c r="Y71" s="8">
@@ -15541,14 +15746,17 @@
       </c>
       <c r="AI71" s="8"/>
       <c r="AJ71" s="8">
-        <f t="shared" ref="AJ71:AJ123" si="41">G71*T71</f>
+        <f t="shared" ref="AJ71:AJ123" si="42">G71*T71</f>
         <v>25.2</v>
       </c>
       <c r="AK71" s="8">
-        <f t="shared" ref="AK71:AK123" si="42">G71*U71</f>
-        <v>0</v>
-      </c>
-      <c r="AL71" s="8"/>
+        <f t="shared" ref="AK71:AK123" si="43">G71*U71</f>
+        <v>0</v>
+      </c>
+      <c r="AL71" s="8">
+        <f t="shared" ref="AL71:AL123" si="44">Q71*G71</f>
+        <v>4.74</v>
+      </c>
       <c r="AM71" s="8"/>
       <c r="AN71" s="8"/>
       <c r="AO71" s="8"/>
@@ -15596,11 +15804,11 @@
         <v>267</v>
       </c>
       <c r="L72" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-84</v>
       </c>
       <c r="M72" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>183</v>
       </c>
       <c r="N72" s="8"/>
@@ -15609,7 +15817,7 @@
       </c>
       <c r="P72" s="8"/>
       <c r="Q72" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>36.6</v>
       </c>
       <c r="R72" s="4">
@@ -15617,11 +15825,11 @@
         <v>322.8</v>
       </c>
       <c r="S72" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>323</v>
       </c>
       <c r="T72" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>194</v>
       </c>
       <c r="U72" s="4">
@@ -15630,11 +15838,11 @@
       </c>
       <c r="V72" s="19"/>
       <c r="W72" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>13.005464480874316</v>
       </c>
       <c r="X72" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>4.1803278688524586</v>
       </c>
       <c r="Y72" s="8">
@@ -15669,14 +15877,17 @@
       </c>
       <c r="AI72" s="8"/>
       <c r="AJ72" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>34.92</v>
       </c>
       <c r="AK72" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>23.22</v>
       </c>
-      <c r="AL72" s="8"/>
+      <c r="AL72" s="8">
+        <f t="shared" si="44"/>
+        <v>6.5880000000000001</v>
+      </c>
       <c r="AM72" s="8"/>
       <c r="AN72" s="8"/>
       <c r="AO72" s="8"/>
@@ -15718,11 +15929,11 @@
         <v>24</v>
       </c>
       <c r="L73" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M73" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N73" s="11">
@@ -15733,26 +15944,26 @@
       </c>
       <c r="P73" s="11"/>
       <c r="Q73" s="11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="R73" s="14"/>
       <c r="S73" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T73" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U73" s="4"/>
       <c r="V73" s="19"/>
       <c r="W73" s="8" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X73" s="11" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y73" s="11">
@@ -15787,14 +15998,17 @@
       </c>
       <c r="AI73" s="11"/>
       <c r="AJ73" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AK73" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL73" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL73" s="8">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
       <c r="AM73" s="8"/>
       <c r="AN73" s="8"/>
       <c r="AO73" s="8"/>
@@ -15836,11 +16050,11 @@
         <v>40.661000000000001</v>
       </c>
       <c r="L74" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M74" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N74" s="11">
@@ -15849,26 +16063,26 @@
       <c r="O74" s="11"/>
       <c r="P74" s="11"/>
       <c r="Q74" s="11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="R74" s="14"/>
       <c r="S74" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T74" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U74" s="4"/>
       <c r="V74" s="19"/>
       <c r="W74" s="8" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X74" s="11" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y74" s="11">
@@ -15903,14 +16117,17 @@
       </c>
       <c r="AI74" s="11"/>
       <c r="AJ74" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AK74" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL74" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL74" s="8">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
       <c r="AM74" s="8"/>
       <c r="AN74" s="8"/>
       <c r="AO74" s="8"/>
@@ -15958,11 +16175,11 @@
         <v>19</v>
       </c>
       <c r="L75" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M75" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>19</v>
       </c>
       <c r="N75" s="8"/>
@@ -15971,7 +16188,7 @@
       </c>
       <c r="P75" s="8"/>
       <c r="Q75" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>3.8</v>
       </c>
       <c r="R75" s="4">
@@ -15979,21 +16196,21 @@
         <v>32.199999999999996</v>
       </c>
       <c r="S75" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>32</v>
       </c>
       <c r="T75" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>32</v>
       </c>
       <c r="U75" s="4"/>
       <c r="V75" s="19"/>
       <c r="W75" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>8.9473684210526319</v>
       </c>
       <c r="X75" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.52631578947368418</v>
       </c>
       <c r="Y75" s="8">
@@ -16030,14 +16247,17 @@
         <v>193</v>
       </c>
       <c r="AJ75" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>7.04</v>
       </c>
       <c r="AK75" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL75" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL75" s="8">
+        <f t="shared" si="44"/>
+        <v>0.83599999999999997</v>
+      </c>
       <c r="AM75" s="8"/>
       <c r="AN75" s="8"/>
       <c r="AO75" s="8"/>
@@ -16073,11 +16293,11 @@
       <c r="J76" s="11"/>
       <c r="K76" s="11"/>
       <c r="L76" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M76" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N76" s="11"/>
@@ -16086,26 +16306,26 @@
       </c>
       <c r="P76" s="11"/>
       <c r="Q76" s="11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="R76" s="14"/>
       <c r="S76" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T76" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U76" s="4"/>
       <c r="V76" s="19"/>
       <c r="W76" s="8" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X76" s="11" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y76" s="11">
@@ -16142,14 +16362,17 @@
         <v>122</v>
       </c>
       <c r="AJ76" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AK76" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL76" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL76" s="8">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
       <c r="AM76" s="8"/>
       <c r="AN76" s="8"/>
       <c r="AO76" s="8"/>
@@ -16197,11 +16420,11 @@
         <v>1129</v>
       </c>
       <c r="L77" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-408</v>
       </c>
       <c r="M77" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>721</v>
       </c>
       <c r="N77" s="8"/>
@@ -16212,26 +16435,26 @@
         <v>925</v>
       </c>
       <c r="Q77" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>144.19999999999999</v>
       </c>
       <c r="R77" s="4"/>
       <c r="S77" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T77" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U77" s="4"/>
       <c r="V77" s="19"/>
       <c r="W77" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>15.825242718446603</v>
       </c>
       <c r="X77" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>15.825242718446603</v>
       </c>
       <c r="Y77" s="8">
@@ -16266,14 +16489,17 @@
       </c>
       <c r="AI77" s="8"/>
       <c r="AJ77" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AK77" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL77" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL77" s="8">
+        <f t="shared" si="44"/>
+        <v>50.469999999999992</v>
+      </c>
       <c r="AM77" s="8"/>
       <c r="AN77" s="8"/>
       <c r="AO77" s="8"/>
@@ -16321,11 +16547,11 @@
         <v>40</v>
       </c>
       <c r="L78" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-18</v>
       </c>
       <c r="M78" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>22</v>
       </c>
       <c r="N78" s="8"/>
@@ -16334,26 +16560,26 @@
       </c>
       <c r="P78" s="8"/>
       <c r="Q78" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="R78" s="4"/>
       <c r="S78" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T78" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U78" s="4"/>
       <c r="V78" s="19"/>
       <c r="W78" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>24.545454545454543</v>
       </c>
       <c r="X78" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>24.545454545454543</v>
       </c>
       <c r="Y78" s="8">
@@ -16390,14 +16616,17 @@
         <v>74</v>
       </c>
       <c r="AJ78" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AK78" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL78" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL78" s="8">
+        <f t="shared" si="44"/>
+        <v>1.54</v>
+      </c>
       <c r="AM78" s="8"/>
       <c r="AN78" s="8"/>
       <c r="AO78" s="8"/>
@@ -16445,11 +16674,11 @@
         <v>169.2</v>
       </c>
       <c r="L79" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>11.38900000000001</v>
       </c>
       <c r="M79" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>180.589</v>
       </c>
       <c r="N79" s="8"/>
@@ -16458,29 +16687,29 @@
       </c>
       <c r="P79" s="8"/>
       <c r="Q79" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>36.117800000000003</v>
       </c>
       <c r="R79" s="4">
-        <f t="shared" ref="R79" si="43">15*Q79-P79-O79-F79</f>
+        <f t="shared" ref="R79" si="45">15*Q79-P79-O79-F79</f>
         <v>43.513000000000034</v>
       </c>
       <c r="S79" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>44</v>
       </c>
       <c r="T79" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>44</v>
       </c>
       <c r="U79" s="4"/>
       <c r="V79" s="19"/>
       <c r="W79" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>15.013483656258133</v>
       </c>
       <c r="X79" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>13.795247772566436</v>
       </c>
       <c r="Y79" s="8">
@@ -16515,14 +16744,17 @@
       </c>
       <c r="AI79" s="8"/>
       <c r="AJ79" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>44</v>
       </c>
       <c r="AK79" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL79" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL79" s="8">
+        <f t="shared" si="44"/>
+        <v>36.117800000000003</v>
+      </c>
       <c r="AM79" s="8"/>
       <c r="AN79" s="8"/>
       <c r="AO79" s="8"/>
@@ -16566,11 +16798,11 @@
         <v>1</v>
       </c>
       <c r="L80" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-1</v>
       </c>
       <c r="M80" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N80" s="11"/>
@@ -16579,26 +16811,26 @@
       </c>
       <c r="P80" s="11"/>
       <c r="Q80" s="11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="R80" s="14"/>
       <c r="S80" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T80" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U80" s="4"/>
       <c r="V80" s="19"/>
       <c r="W80" s="8" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X80" s="11" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y80" s="11">
@@ -16635,14 +16867,17 @@
         <v>74</v>
       </c>
       <c r="AJ80" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AK80" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL80" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL80" s="8">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
       <c r="AM80" s="8"/>
       <c r="AN80" s="8"/>
       <c r="AO80" s="8"/>
@@ -16690,11 +16925,11 @@
         <v>312.10000000000002</v>
       </c>
       <c r="L81" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>19.127999999999986</v>
       </c>
       <c r="M81" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>331.22800000000001</v>
       </c>
       <c r="N81" s="8"/>
@@ -16703,32 +16938,32 @@
       </c>
       <c r="P81" s="8"/>
       <c r="Q81" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>66.245599999999996</v>
       </c>
       <c r="R81" s="4">
-        <f t="shared" ref="R81:R86" si="44">15*Q81-P81-O81-F81</f>
+        <f t="shared" ref="R81:R86" si="46">15*Q81-P81-O81-F81</f>
         <v>253.98899999999992</v>
       </c>
       <c r="S81" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>254</v>
       </c>
       <c r="T81" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>152</v>
       </c>
       <c r="U81" s="4">
-        <f t="shared" ref="U81:U84" si="45">ROUND(S81*$U$1,0)</f>
+        <f t="shared" ref="U81:U84" si="47">ROUND(S81*$U$1,0)</f>
         <v>102</v>
       </c>
       <c r="V81" s="19"/>
       <c r="W81" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>15.000166048763996</v>
       </c>
       <c r="X81" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>11.165949134734987</v>
       </c>
       <c r="Y81" s="8">
@@ -16763,14 +16998,17 @@
       </c>
       <c r="AI81" s="8"/>
       <c r="AJ81" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>152</v>
       </c>
       <c r="AK81" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>102</v>
       </c>
-      <c r="AL81" s="8"/>
+      <c r="AL81" s="8">
+        <f t="shared" si="44"/>
+        <v>66.245599999999996</v>
+      </c>
       <c r="AM81" s="8"/>
       <c r="AN81" s="8"/>
       <c r="AO81" s="8"/>
@@ -16818,11 +17056,11 @@
         <v>1590</v>
       </c>
       <c r="L82" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-616</v>
       </c>
       <c r="M82" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>942</v>
       </c>
       <c r="N82" s="8">
@@ -16835,32 +17073,32 @@
         <v>1235</v>
       </c>
       <c r="Q82" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>188.4</v>
       </c>
       <c r="R82" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>333</v>
       </c>
       <c r="S82" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>333</v>
       </c>
       <c r="T82" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>200</v>
       </c>
       <c r="U82" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>133</v>
       </c>
       <c r="V82" s="19"/>
       <c r="W82" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>15</v>
       </c>
       <c r="X82" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>13.232484076433121</v>
       </c>
       <c r="Y82" s="8">
@@ -16897,14 +17135,17 @@
         <v>137</v>
       </c>
       <c r="AJ82" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>70</v>
       </c>
       <c r="AK82" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>46.55</v>
       </c>
-      <c r="AL82" s="8"/>
+      <c r="AL82" s="8">
+        <f t="shared" si="44"/>
+        <v>65.94</v>
+      </c>
       <c r="AM82" s="8"/>
       <c r="AN82" s="8"/>
       <c r="AO82" s="8"/>
@@ -16952,11 +17193,11 @@
         <v>187</v>
       </c>
       <c r="L83" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-5</v>
       </c>
       <c r="M83" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>122</v>
       </c>
       <c r="N83" s="8">
@@ -16969,32 +17210,32 @@
         <v>109</v>
       </c>
       <c r="Q83" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>24.4</v>
       </c>
       <c r="R83" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>166</v>
       </c>
       <c r="S83" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>166</v>
       </c>
       <c r="T83" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>100</v>
       </c>
       <c r="U83" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>66</v>
       </c>
       <c r="V83" s="19"/>
       <c r="W83" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>15</v>
       </c>
       <c r="X83" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>8.1967213114754109</v>
       </c>
       <c r="Y83" s="8">
@@ -17029,14 +17270,17 @@
       </c>
       <c r="AI83" s="8"/>
       <c r="AJ83" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>30</v>
       </c>
       <c r="AK83" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>19.8</v>
       </c>
-      <c r="AL83" s="8"/>
+      <c r="AL83" s="8">
+        <f t="shared" si="44"/>
+        <v>7.3199999999999994</v>
+      </c>
       <c r="AM83" s="8"/>
       <c r="AN83" s="8"/>
       <c r="AO83" s="8"/>
@@ -17084,11 +17328,11 @@
         <v>92</v>
       </c>
       <c r="L84" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-41</v>
       </c>
       <c r="M84" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>51</v>
       </c>
       <c r="N84" s="8"/>
@@ -17097,11 +17341,11 @@
       </c>
       <c r="P84" s="8"/>
       <c r="Q84" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>10.199999999999999</v>
       </c>
       <c r="R84" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>94</v>
       </c>
       <c r="S84" s="4">
@@ -17109,11 +17353,11 @@
         <v>130</v>
       </c>
       <c r="T84" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>78</v>
       </c>
       <c r="U84" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>52</v>
       </c>
       <c r="V84" s="19">
@@ -17121,11 +17365,11 @@
         <v>130</v>
       </c>
       <c r="W84" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>18.529411764705884</v>
       </c>
       <c r="X84" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>5.7843137254901968</v>
       </c>
       <c r="Y84" s="8">
@@ -17160,14 +17404,17 @@
       </c>
       <c r="AI84" s="8"/>
       <c r="AJ84" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>23.4</v>
       </c>
       <c r="AK84" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>15.6</v>
       </c>
-      <c r="AL84" s="8"/>
+      <c r="AL84" s="8">
+        <f t="shared" si="44"/>
+        <v>3.0599999999999996</v>
+      </c>
       <c r="AM84" s="8"/>
       <c r="AN84" s="8"/>
       <c r="AO84" s="8"/>
@@ -17215,11 +17462,11 @@
         <v>153</v>
       </c>
       <c r="L85" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-21</v>
       </c>
       <c r="M85" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>100</v>
       </c>
       <c r="N85" s="8">
@@ -17232,29 +17479,29 @@
         <v>106</v>
       </c>
       <c r="Q85" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>20</v>
       </c>
       <c r="R85" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>48</v>
       </c>
       <c r="S85" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>48</v>
       </c>
       <c r="T85" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>48</v>
       </c>
       <c r="U85" s="4"/>
       <c r="V85" s="19"/>
       <c r="W85" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>15</v>
       </c>
       <c r="X85" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>12.6</v>
       </c>
       <c r="Y85" s="8">
@@ -17289,14 +17536,17 @@
       </c>
       <c r="AI85" s="8"/>
       <c r="AJ85" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>13.440000000000001</v>
       </c>
       <c r="AK85" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL85" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL85" s="8">
+        <f t="shared" si="44"/>
+        <v>5.6000000000000005</v>
+      </c>
       <c r="AM85" s="8"/>
       <c r="AN85" s="8"/>
       <c r="AO85" s="8"/>
@@ -17344,11 +17594,11 @@
         <v>429</v>
       </c>
       <c r="L86" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-156</v>
       </c>
       <c r="M86" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>225</v>
       </c>
       <c r="N86" s="8">
@@ -17361,29 +17611,29 @@
         <v>353</v>
       </c>
       <c r="Q86" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>45</v>
       </c>
       <c r="R86" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>26</v>
       </c>
       <c r="S86" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>26</v>
       </c>
       <c r="T86" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>26</v>
       </c>
       <c r="U86" s="4"/>
       <c r="V86" s="19"/>
       <c r="W86" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>15</v>
       </c>
       <c r="X86" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>14.422222222222222</v>
       </c>
       <c r="Y86" s="8">
@@ -17420,14 +17670,17 @@
         <v>142</v>
       </c>
       <c r="AJ86" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>7.2800000000000011</v>
       </c>
       <c r="AK86" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL86" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL86" s="8">
+        <f t="shared" si="44"/>
+        <v>12.600000000000001</v>
+      </c>
       <c r="AM86" s="8"/>
       <c r="AN86" s="8"/>
       <c r="AO86" s="8"/>
@@ -17465,11 +17718,11 @@
       <c r="J87" s="11"/>
       <c r="K87" s="11"/>
       <c r="L87" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M87" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N87" s="11"/>
@@ -17478,26 +17731,26 @@
       </c>
       <c r="P87" s="11"/>
       <c r="Q87" s="11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="R87" s="14"/>
       <c r="S87" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T87" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U87" s="4"/>
       <c r="V87" s="19"/>
       <c r="W87" s="8" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X87" s="11" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y87" s="11">
@@ -17532,14 +17785,17 @@
       </c>
       <c r="AI87" s="11"/>
       <c r="AJ87" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AK87" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL87" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL87" s="8">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
       <c r="AM87" s="8"/>
       <c r="AN87" s="8"/>
       <c r="AO87" s="8"/>
@@ -17587,11 +17843,11 @@
         <v>494</v>
       </c>
       <c r="L88" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-213</v>
       </c>
       <c r="M88" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>281</v>
       </c>
       <c r="N88" s="8"/>
@@ -17602,32 +17858,32 @@
         <v>184</v>
       </c>
       <c r="Q88" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>56.2</v>
       </c>
       <c r="R88" s="4">
-        <f t="shared" ref="R88:R89" si="46">15*Q88-P88-O88-F88</f>
+        <f t="shared" ref="R88:R89" si="48">15*Q88-P88-O88-F88</f>
         <v>452</v>
       </c>
       <c r="S88" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>452</v>
       </c>
       <c r="T88" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>271</v>
       </c>
       <c r="U88" s="4">
-        <f t="shared" ref="U88:U89" si="47">ROUND(S88*$U$1,0)</f>
+        <f t="shared" ref="U88:U89" si="49">ROUND(S88*$U$1,0)</f>
         <v>181</v>
       </c>
       <c r="V88" s="19"/>
       <c r="W88" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>15</v>
       </c>
       <c r="X88" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>6.9572953736654801</v>
       </c>
       <c r="Y88" s="8">
@@ -17662,14 +17918,17 @@
       </c>
       <c r="AI88" s="8"/>
       <c r="AJ88" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>75.88000000000001</v>
       </c>
       <c r="AK88" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>50.680000000000007</v>
       </c>
-      <c r="AL88" s="8"/>
+      <c r="AL88" s="8">
+        <f t="shared" si="44"/>
+        <v>15.736000000000002</v>
+      </c>
       <c r="AM88" s="8"/>
       <c r="AN88" s="8"/>
       <c r="AO88" s="8"/>
@@ -17717,11 +17976,11 @@
         <v>509</v>
       </c>
       <c r="L89" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-128</v>
       </c>
       <c r="M89" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>381</v>
       </c>
       <c r="N89" s="8"/>
@@ -17732,32 +17991,32 @@
         <v>487</v>
       </c>
       <c r="Q89" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>76.2</v>
       </c>
       <c r="R89" s="4">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>256</v>
       </c>
       <c r="S89" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>256</v>
       </c>
       <c r="T89" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>154</v>
       </c>
       <c r="U89" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>102</v>
       </c>
       <c r="V89" s="19"/>
       <c r="W89" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>15</v>
       </c>
       <c r="X89" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>11.640419947506562</v>
       </c>
       <c r="Y89" s="8">
@@ -17792,14 +18051,17 @@
       </c>
       <c r="AI89" s="8"/>
       <c r="AJ89" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>61.6</v>
       </c>
       <c r="AK89" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>40.800000000000004</v>
       </c>
-      <c r="AL89" s="8"/>
+      <c r="AL89" s="8">
+        <f t="shared" si="44"/>
+        <v>30.480000000000004</v>
+      </c>
       <c r="AM89" s="8"/>
       <c r="AN89" s="8"/>
       <c r="AO89" s="8"/>
@@ -17841,11 +18103,11 @@
         <v>30.477</v>
       </c>
       <c r="L90" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M90" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N90" s="11">
@@ -17854,26 +18116,26 @@
       <c r="O90" s="11"/>
       <c r="P90" s="11"/>
       <c r="Q90" s="11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="R90" s="14"/>
       <c r="S90" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T90" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U90" s="4"/>
       <c r="V90" s="19"/>
       <c r="W90" s="8" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X90" s="11" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y90" s="11">
@@ -17908,14 +18170,17 @@
       </c>
       <c r="AI90" s="11"/>
       <c r="AJ90" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AK90" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL90" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL90" s="8">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
       <c r="AM90" s="8"/>
       <c r="AN90" s="8"/>
       <c r="AO90" s="8"/>
@@ -17955,11 +18220,11 @@
         <v>3</v>
       </c>
       <c r="L91" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-3</v>
       </c>
       <c r="M91" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N91" s="11"/>
@@ -17968,26 +18233,26 @@
       </c>
       <c r="P91" s="11"/>
       <c r="Q91" s="11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="R91" s="14"/>
       <c r="S91" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T91" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U91" s="4"/>
       <c r="V91" s="19"/>
       <c r="W91" s="8" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X91" s="11" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y91" s="11">
@@ -18022,14 +18287,17 @@
       </c>
       <c r="AI91" s="11"/>
       <c r="AJ91" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AK91" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL91" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL91" s="8">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
       <c r="AM91" s="8"/>
       <c r="AN91" s="8"/>
       <c r="AO91" s="8"/>
@@ -18077,11 +18345,11 @@
         <v>175.488</v>
       </c>
       <c r="L92" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-30.710000000000008</v>
       </c>
       <c r="M92" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>144.77799999999999</v>
       </c>
       <c r="N92" s="8"/>
@@ -18092,7 +18360,7 @@
         <v>62</v>
       </c>
       <c r="Q92" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>28.955599999999997</v>
       </c>
       <c r="R92" s="4">
@@ -18100,11 +18368,11 @@
         <v>218.79619999999994</v>
       </c>
       <c r="S92" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>219</v>
       </c>
       <c r="T92" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>131</v>
       </c>
       <c r="U92" s="4">
@@ -18113,11 +18381,11 @@
       </c>
       <c r="V92" s="19"/>
       <c r="W92" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>12.007038362182101</v>
       </c>
       <c r="X92" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>4.4437345453038448</v>
       </c>
       <c r="Y92" s="8">
@@ -18152,14 +18420,17 @@
       </c>
       <c r="AI92" s="8"/>
       <c r="AJ92" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>131</v>
       </c>
       <c r="AK92" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>88</v>
       </c>
-      <c r="AL92" s="8"/>
+      <c r="AL92" s="8">
+        <f t="shared" si="44"/>
+        <v>28.955599999999997</v>
+      </c>
       <c r="AM92" s="8"/>
       <c r="AN92" s="8"/>
       <c r="AO92" s="8"/>
@@ -18201,11 +18472,11 @@
         <v>24</v>
       </c>
       <c r="L93" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M93" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N93" s="11">
@@ -18214,26 +18485,26 @@
       <c r="O93" s="11"/>
       <c r="P93" s="11"/>
       <c r="Q93" s="11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="R93" s="14"/>
       <c r="S93" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T93" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U93" s="4"/>
       <c r="V93" s="19"/>
       <c r="W93" s="8" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X93" s="11" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y93" s="11">
@@ -18268,14 +18539,17 @@
       </c>
       <c r="AI93" s="11"/>
       <c r="AJ93" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AK93" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL93" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL93" s="8">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
       <c r="AM93" s="8"/>
       <c r="AN93" s="8"/>
       <c r="AO93" s="8"/>
@@ -18323,11 +18597,11 @@
         <v>72</v>
       </c>
       <c r="L94" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M94" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>72</v>
       </c>
       <c r="N94" s="8"/>
@@ -18336,7 +18610,7 @@
       </c>
       <c r="P94" s="8"/>
       <c r="Q94" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>14.4</v>
       </c>
       <c r="R94" s="4">
@@ -18344,24 +18618,24 @@
         <v>112</v>
       </c>
       <c r="S94" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>112</v>
       </c>
       <c r="T94" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>67</v>
       </c>
       <c r="U94" s="4">
-        <f t="shared" ref="U94:U100" si="48">ROUND(S94*$U$1,0)</f>
+        <f t="shared" ref="U94:U100" si="50">ROUND(S94*$U$1,0)</f>
         <v>45</v>
       </c>
       <c r="V94" s="19"/>
       <c r="W94" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>10</v>
       </c>
       <c r="X94" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>2.2222222222222223</v>
       </c>
       <c r="Y94" s="8">
@@ -18398,14 +18672,17 @@
         <v>155</v>
       </c>
       <c r="AJ94" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>22.646000000000001</v>
       </c>
       <c r="AK94" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>15.21</v>
       </c>
-      <c r="AL94" s="8"/>
+      <c r="AL94" s="8">
+        <f t="shared" si="44"/>
+        <v>4.8672000000000004</v>
+      </c>
       <c r="AM94" s="8"/>
       <c r="AN94" s="8"/>
       <c r="AO94" s="8"/>
@@ -18451,11 +18728,11 @@
         <v>63</v>
       </c>
       <c r="L95" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M95" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>63</v>
       </c>
       <c r="N95" s="8"/>
@@ -18464,7 +18741,7 @@
       </c>
       <c r="P95" s="8"/>
       <c r="Q95" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>12.6</v>
       </c>
       <c r="R95" s="4">
@@ -18472,24 +18749,24 @@
         <v>101.39999999999999</v>
       </c>
       <c r="S95" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>101</v>
       </c>
       <c r="T95" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>61</v>
       </c>
       <c r="U95" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>40</v>
       </c>
       <c r="V95" s="19"/>
       <c r="W95" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>8.9682539682539684</v>
       </c>
       <c r="X95" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.95238095238095244</v>
       </c>
       <c r="Y95" s="8">
@@ -18526,14 +18803,17 @@
         <v>155</v>
       </c>
       <c r="AJ95" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>19.824999999999999</v>
       </c>
       <c r="AK95" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>13</v>
       </c>
-      <c r="AL95" s="8"/>
+      <c r="AL95" s="8">
+        <f t="shared" si="44"/>
+        <v>4.0949999999999998</v>
+      </c>
       <c r="AM95" s="8"/>
       <c r="AN95" s="8"/>
       <c r="AO95" s="8"/>
@@ -18581,11 +18861,11 @@
         <v>351</v>
       </c>
       <c r="L96" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-149</v>
       </c>
       <c r="M96" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>202</v>
       </c>
       <c r="N96" s="8"/>
@@ -18594,7 +18874,7 @@
       </c>
       <c r="P96" s="8"/>
       <c r="Q96" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>40.4</v>
       </c>
       <c r="R96" s="4">
@@ -18602,24 +18882,24 @@
         <v>364.6</v>
       </c>
       <c r="S96" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>365</v>
       </c>
       <c r="T96" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>219</v>
       </c>
       <c r="U96" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>146</v>
       </c>
       <c r="V96" s="19"/>
       <c r="W96" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>14.009900990099011</v>
       </c>
       <c r="X96" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>4.9752475247524757</v>
       </c>
       <c r="Y96" s="8">
@@ -18654,14 +18934,17 @@
       </c>
       <c r="AI96" s="8"/>
       <c r="AJ96" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>26.279999999999998</v>
       </c>
       <c r="AK96" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>17.52</v>
       </c>
-      <c r="AL96" s="8"/>
+      <c r="AL96" s="8">
+        <f t="shared" si="44"/>
+        <v>4.8479999999999999</v>
+      </c>
       <c r="AM96" s="8"/>
       <c r="AN96" s="8"/>
       <c r="AO96" s="8"/>
@@ -18709,11 +18992,11 @@
         <v>101</v>
       </c>
       <c r="L97" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-2</v>
       </c>
       <c r="M97" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>99</v>
       </c>
       <c r="N97" s="8"/>
@@ -18722,7 +19005,7 @@
       </c>
       <c r="P97" s="8"/>
       <c r="Q97" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>19.8</v>
       </c>
       <c r="R97" s="4">
@@ -18730,15 +19013,15 @@
         <v>162</v>
       </c>
       <c r="S97" s="4">
-        <f t="shared" ref="S97:S99" si="49">V97</f>
+        <f t="shared" ref="S97:S99" si="51">V97</f>
         <v>190</v>
       </c>
       <c r="T97" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>114</v>
       </c>
       <c r="U97" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>76</v>
       </c>
       <c r="V97" s="19">
@@ -18746,11 +19029,11 @@
         <v>190</v>
       </c>
       <c r="W97" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>11.414141414141413</v>
       </c>
       <c r="X97" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1.8181818181818181</v>
       </c>
       <c r="Y97" s="8">
@@ -18787,14 +19070,17 @@
         <v>155</v>
       </c>
       <c r="AJ97" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>17.099999999999998</v>
       </c>
       <c r="AK97" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>11.4</v>
       </c>
-      <c r="AL97" s="8"/>
+      <c r="AL97" s="8">
+        <f t="shared" si="44"/>
+        <v>2.97</v>
+      </c>
       <c r="AM97" s="8"/>
       <c r="AN97" s="8"/>
       <c r="AO97" s="8"/>
@@ -18840,11 +19126,11 @@
         <v>103</v>
       </c>
       <c r="L98" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-13</v>
       </c>
       <c r="M98" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>90</v>
       </c>
       <c r="N98" s="8"/>
@@ -18853,7 +19139,7 @@
       </c>
       <c r="P98" s="8"/>
       <c r="Q98" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>18</v>
       </c>
       <c r="R98" s="4">
@@ -18861,15 +19147,15 @@
         <v>152</v>
       </c>
       <c r="S98" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>190</v>
       </c>
       <c r="T98" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>114</v>
       </c>
       <c r="U98" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>76</v>
       </c>
       <c r="V98" s="19">
@@ -18877,11 +19163,11 @@
         <v>190</v>
       </c>
       <c r="W98" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>11.111111111111111</v>
       </c>
       <c r="X98" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.55555555555555558</v>
       </c>
       <c r="Y98" s="8">
@@ -18918,14 +19204,17 @@
         <v>155</v>
       </c>
       <c r="AJ98" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>17.099999999999998</v>
       </c>
       <c r="AK98" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>11.4</v>
       </c>
-      <c r="AL98" s="8"/>
+      <c r="AL98" s="8">
+        <f t="shared" si="44"/>
+        <v>2.6999999999999997</v>
+      </c>
       <c r="AM98" s="8"/>
       <c r="AN98" s="8"/>
       <c r="AO98" s="8"/>
@@ -18973,11 +19262,11 @@
         <v>383</v>
       </c>
       <c r="L99" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-124</v>
       </c>
       <c r="M99" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>259</v>
       </c>
       <c r="N99" s="8"/>
@@ -18988,23 +19277,23 @@
         <v>298</v>
       </c>
       <c r="Q99" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>51.8</v>
       </c>
       <c r="R99" s="4">
-        <f t="shared" ref="R99:R100" si="50">15*Q99-P99-O99-F99</f>
+        <f t="shared" ref="R99:R100" si="52">15*Q99-P99-O99-F99</f>
         <v>228</v>
       </c>
       <c r="S99" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>250</v>
       </c>
       <c r="T99" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>150</v>
       </c>
       <c r="U99" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>100</v>
       </c>
       <c r="V99" s="19">
@@ -19012,11 +19301,11 @@
         <v>250</v>
       </c>
       <c r="W99" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>15.424710424710426</v>
       </c>
       <c r="X99" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>10.598455598455599</v>
       </c>
       <c r="Y99" s="8">
@@ -19051,14 +19340,17 @@
       </c>
       <c r="AI99" s="8"/>
       <c r="AJ99" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>49.5</v>
       </c>
       <c r="AK99" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>33</v>
       </c>
-      <c r="AL99" s="8"/>
+      <c r="AL99" s="8">
+        <f t="shared" si="44"/>
+        <v>17.094000000000001</v>
+      </c>
       <c r="AM99" s="8"/>
       <c r="AN99" s="8"/>
       <c r="AO99" s="8"/>
@@ -19106,11 +19398,11 @@
         <v>557</v>
       </c>
       <c r="L100" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-16</v>
       </c>
       <c r="M100" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>541</v>
       </c>
       <c r="N100" s="8"/>
@@ -19121,32 +19413,32 @@
         <v>58</v>
       </c>
       <c r="Q100" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>108.2</v>
       </c>
       <c r="R100" s="4">
+        <f t="shared" si="52"/>
+        <v>949</v>
+      </c>
+      <c r="S100" s="4">
+        <f t="shared" si="39"/>
+        <v>949</v>
+      </c>
+      <c r="T100" s="4">
+        <f t="shared" si="40"/>
+        <v>569</v>
+      </c>
+      <c r="U100" s="4">
         <f t="shared" si="50"/>
-        <v>949</v>
-      </c>
-      <c r="S100" s="4">
-        <f t="shared" si="38"/>
-        <v>949</v>
-      </c>
-      <c r="T100" s="4">
-        <f t="shared" si="39"/>
-        <v>569</v>
-      </c>
-      <c r="U100" s="4">
-        <f t="shared" si="48"/>
         <v>380</v>
       </c>
       <c r="V100" s="19"/>
       <c r="W100" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>15</v>
       </c>
       <c r="X100" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>6.2292051756007396</v>
       </c>
       <c r="Y100" s="8">
@@ -19181,14 +19473,17 @@
       </c>
       <c r="AI100" s="8"/>
       <c r="AJ100" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>85.35</v>
       </c>
       <c r="AK100" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>57</v>
       </c>
-      <c r="AL100" s="8"/>
+      <c r="AL100" s="8">
+        <f t="shared" si="44"/>
+        <v>16.23</v>
+      </c>
       <c r="AM100" s="8"/>
       <c r="AN100" s="8"/>
       <c r="AO100" s="8"/>
@@ -19238,11 +19533,11 @@
         <v>83</v>
       </c>
       <c r="L101" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-53</v>
       </c>
       <c r="M101" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>30</v>
       </c>
       <c r="N101" s="8"/>
@@ -19251,26 +19546,26 @@
       </c>
       <c r="P101" s="8"/>
       <c r="Q101" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>6</v>
       </c>
       <c r="R101" s="4"/>
       <c r="S101" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T101" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U101" s="4"/>
       <c r="V101" s="19"/>
       <c r="W101" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>96.333333333333329</v>
       </c>
       <c r="X101" s="8">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>96.333333333333329</v>
       </c>
       <c r="Y101" s="8">
@@ -19307,14 +19602,17 @@
         <v>159</v>
       </c>
       <c r="AJ101" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AK101" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL101" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL101" s="8">
+        <f t="shared" si="44"/>
+        <v>2.46</v>
+      </c>
       <c r="AM101" s="8"/>
       <c r="AN101" s="8"/>
       <c r="AO101" s="8"/>
@@ -19354,11 +19652,11 @@
       <c r="J102" s="11"/>
       <c r="K102" s="11"/>
       <c r="L102" s="11">
-        <f t="shared" ref="L102:L123" si="51">E102-K102</f>
+        <f t="shared" ref="L102:L123" si="53">E102-K102</f>
         <v>0</v>
       </c>
       <c r="M102" s="11">
-        <f t="shared" ref="M102:M123" si="52">E102-N102</f>
+        <f t="shared" ref="M102:M123" si="54">E102-N102</f>
         <v>0</v>
       </c>
       <c r="N102" s="11"/>
@@ -19367,26 +19665,26 @@
       </c>
       <c r="P102" s="11"/>
       <c r="Q102" s="11">
-        <f t="shared" ref="Q102:Q123" si="53">M102/5</f>
+        <f t="shared" ref="Q102:Q123" si="55">M102/5</f>
         <v>0</v>
       </c>
       <c r="R102" s="14"/>
       <c r="S102" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T102" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U102" s="4"/>
       <c r="V102" s="19"/>
       <c r="W102" s="8" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X102" s="11" t="e">
-        <f t="shared" ref="X102:X123" si="54">(F102+O102+P102)/Q102</f>
+        <f t="shared" ref="X102:X123" si="56">(F102+O102+P102)/Q102</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Y102" s="11">
@@ -19421,14 +19719,17 @@
       </c>
       <c r="AI102" s="11"/>
       <c r="AJ102" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AK102" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL102" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL102" s="8">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
       <c r="AM102" s="8"/>
       <c r="AN102" s="8"/>
       <c r="AO102" s="8"/>
@@ -19476,11 +19777,11 @@
         <v>163</v>
       </c>
       <c r="L103" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-9</v>
       </c>
       <c r="M103" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>154</v>
       </c>
       <c r="N103" s="8"/>
@@ -19489,19 +19790,19 @@
       </c>
       <c r="P103" s="8"/>
       <c r="Q103" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>30.8</v>
       </c>
       <c r="R103" s="4">
-        <f t="shared" ref="R103:R110" si="55">15*Q103-P103-O103-F103</f>
+        <f t="shared" ref="R103:R110" si="57">15*Q103-P103-O103-F103</f>
         <v>258</v>
       </c>
       <c r="S103" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>258</v>
       </c>
       <c r="T103" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>155</v>
       </c>
       <c r="U103" s="4">
@@ -19510,11 +19811,11 @@
       </c>
       <c r="V103" s="19"/>
       <c r="W103" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>15</v>
       </c>
       <c r="X103" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>6.6233766233766236</v>
       </c>
       <c r="Y103" s="8">
@@ -19549,14 +19850,17 @@
       </c>
       <c r="AI103" s="8"/>
       <c r="AJ103" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>40.300000000000004</v>
       </c>
       <c r="AK103" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>26.78</v>
       </c>
-      <c r="AL103" s="8"/>
+      <c r="AL103" s="8">
+        <f t="shared" si="44"/>
+        <v>8.0080000000000009</v>
+      </c>
       <c r="AM103" s="8"/>
       <c r="AN103" s="8"/>
       <c r="AO103" s="8"/>
@@ -19604,11 +19908,11 @@
         <v>60.6</v>
       </c>
       <c r="L104" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>3.5689999999999955</v>
       </c>
       <c r="M104" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>64.168999999999997</v>
       </c>
       <c r="N104" s="8"/>
@@ -19617,29 +19921,29 @@
       </c>
       <c r="P104" s="8"/>
       <c r="Q104" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>12.8338</v>
       </c>
       <c r="R104" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>85.864000000000004</v>
       </c>
       <c r="S104" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>86</v>
       </c>
       <c r="T104" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>86</v>
       </c>
       <c r="U104" s="4"/>
       <c r="V104" s="19"/>
       <c r="W104" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>15.010597017251321</v>
       </c>
       <c r="X104" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>8.3095419906808576</v>
       </c>
       <c r="Y104" s="8">
@@ -19676,14 +19980,17 @@
         <v>155</v>
       </c>
       <c r="AJ104" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>86</v>
       </c>
       <c r="AK104" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL104" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL104" s="8">
+        <f t="shared" si="44"/>
+        <v>12.8338</v>
+      </c>
       <c r="AM104" s="8"/>
       <c r="AN104" s="8"/>
       <c r="AO104" s="8"/>
@@ -19731,11 +20038,11 @@
         <v>108</v>
       </c>
       <c r="L105" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-6</v>
       </c>
       <c r="M105" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>102</v>
       </c>
       <c r="N105" s="8"/>
@@ -19744,11 +20051,11 @@
       </c>
       <c r="P105" s="8"/>
       <c r="Q105" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>20.399999999999999</v>
       </c>
       <c r="R105" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>104</v>
       </c>
       <c r="S105" s="4">
@@ -19756,7 +20063,7 @@
         <v>140</v>
       </c>
       <c r="T105" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>84</v>
       </c>
       <c r="U105" s="4">
@@ -19768,11 +20075,11 @@
         <v>140</v>
       </c>
       <c r="W105" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>16.764705882352942</v>
       </c>
       <c r="X105" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>9.9019607843137258</v>
       </c>
       <c r="Y105" s="8">
@@ -19807,14 +20114,17 @@
       </c>
       <c r="AI105" s="8"/>
       <c r="AJ105" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>26.04</v>
       </c>
       <c r="AK105" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>17.36</v>
       </c>
-      <c r="AL105" s="8"/>
+      <c r="AL105" s="8">
+        <f t="shared" si="44"/>
+        <v>6.3239999999999998</v>
+      </c>
       <c r="AM105" s="8"/>
       <c r="AN105" s="8"/>
       <c r="AO105" s="8"/>
@@ -19862,11 +20172,11 @@
         <v>23.1</v>
       </c>
       <c r="L106" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-5.32</v>
       </c>
       <c r="M106" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>17.78</v>
       </c>
       <c r="N106" s="8"/>
@@ -19875,29 +20185,29 @@
       </c>
       <c r="P106" s="8"/>
       <c r="Q106" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>3.556</v>
       </c>
       <c r="R106" s="4">
-        <f t="shared" ref="R106" si="56">12*Q106-P106-O106-F106</f>
+        <f t="shared" ref="R106" si="58">12*Q106-P106-O106-F106</f>
         <v>30.075999999999997</v>
       </c>
       <c r="S106" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>30</v>
       </c>
       <c r="T106" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>30</v>
       </c>
       <c r="U106" s="4"/>
       <c r="V106" s="19"/>
       <c r="W106" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>11.978627671541059</v>
       </c>
       <c r="X106" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>3.5421822272215975</v>
       </c>
       <c r="Y106" s="8">
@@ -19934,14 +20244,17 @@
         <v>155</v>
       </c>
       <c r="AJ106" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>30</v>
       </c>
       <c r="AK106" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL106" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL106" s="8">
+        <f t="shared" si="44"/>
+        <v>3.556</v>
+      </c>
       <c r="AM106" s="8"/>
       <c r="AN106" s="8"/>
       <c r="AO106" s="8"/>
@@ -19989,11 +20302,11 @@
         <v>278</v>
       </c>
       <c r="L107" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-10</v>
       </c>
       <c r="M107" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>244</v>
       </c>
       <c r="N107" s="8">
@@ -20004,7 +20317,7 @@
       </c>
       <c r="P107" s="8"/>
       <c r="Q107" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>48.8</v>
       </c>
       <c r="R107" s="4">
@@ -20012,11 +20325,11 @@
         <v>450.4</v>
       </c>
       <c r="S107" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>450</v>
       </c>
       <c r="T107" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>270</v>
       </c>
       <c r="U107" s="4">
@@ -20025,11 +20338,11 @@
       </c>
       <c r="V107" s="19"/>
       <c r="W107" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>12.991803278688526</v>
       </c>
       <c r="X107" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>3.7704918032786887</v>
       </c>
       <c r="Y107" s="8">
@@ -20064,14 +20377,17 @@
       </c>
       <c r="AI107" s="8"/>
       <c r="AJ107" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>108</v>
       </c>
       <c r="AK107" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>72</v>
       </c>
-      <c r="AL107" s="8"/>
+      <c r="AL107" s="8">
+        <f t="shared" si="44"/>
+        <v>19.52</v>
+      </c>
       <c r="AM107" s="8"/>
       <c r="AN107" s="8"/>
       <c r="AO107" s="8"/>
@@ -20117,11 +20433,11 @@
         <v>363</v>
       </c>
       <c r="L108" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-271</v>
       </c>
       <c r="M108" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>60</v>
       </c>
       <c r="N108" s="8">
@@ -20134,26 +20450,26 @@
         <v>138</v>
       </c>
       <c r="Q108" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>12</v>
       </c>
       <c r="R108" s="4"/>
       <c r="S108" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T108" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U108" s="4"/>
       <c r="V108" s="19"/>
       <c r="W108" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>54.166666666666664</v>
       </c>
       <c r="X108" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>54.166666666666664</v>
       </c>
       <c r="Y108" s="8">
@@ -20188,14 +20504,17 @@
       </c>
       <c r="AI108" s="8"/>
       <c r="AJ108" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AK108" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL108" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL108" s="8">
+        <f t="shared" si="44"/>
+        <v>4.1999999999999993</v>
+      </c>
       <c r="AM108" s="8"/>
       <c r="AN108" s="8"/>
       <c r="AO108" s="8"/>
@@ -20241,11 +20560,11 @@
         <v>48.14</v>
       </c>
       <c r="L109" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-25.212</v>
       </c>
       <c r="M109" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>22.928000000000001</v>
       </c>
       <c r="N109" s="8"/>
@@ -20254,7 +20573,7 @@
       </c>
       <c r="P109" s="8"/>
       <c r="Q109" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>4.5856000000000003</v>
       </c>
       <c r="R109" s="4">
@@ -20262,21 +20581,21 @@
         <v>41.270400000000002</v>
       </c>
       <c r="S109" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>41</v>
       </c>
       <c r="T109" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>41</v>
       </c>
       <c r="U109" s="4"/>
       <c r="V109" s="19"/>
       <c r="W109" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>8.9410327983251907</v>
       </c>
       <c r="X109" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="Y109" s="8">
@@ -20313,14 +20632,17 @@
         <v>192</v>
       </c>
       <c r="AJ109" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>41</v>
       </c>
       <c r="AK109" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL109" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL109" s="8">
+        <f t="shared" si="44"/>
+        <v>4.5856000000000003</v>
+      </c>
       <c r="AM109" s="8"/>
       <c r="AN109" s="8"/>
       <c r="AO109" s="8"/>
@@ -20368,11 +20690,11 @@
         <v>7.1</v>
       </c>
       <c r="L110" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0.52899999999999991</v>
       </c>
       <c r="M110" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>7.6289999999999996</v>
       </c>
       <c r="N110" s="8"/>
@@ -20381,29 +20703,29 @@
       </c>
       <c r="P110" s="8"/>
       <c r="Q110" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>1.5257999999999998</v>
       </c>
       <c r="R110" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>4.3939999999999984</v>
       </c>
       <c r="S110" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>4</v>
       </c>
       <c r="T110" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>4</v>
       </c>
       <c r="U110" s="4"/>
       <c r="V110" s="19"/>
       <c r="W110" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>14.741774806658803</v>
       </c>
       <c r="X110" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>12.120199239743085</v>
       </c>
       <c r="Y110" s="8">
@@ -20438,14 +20760,17 @@
       </c>
       <c r="AI110" s="8"/>
       <c r="AJ110" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>4</v>
       </c>
       <c r="AK110" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL110" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL110" s="8">
+        <f t="shared" si="44"/>
+        <v>1.5257999999999998</v>
+      </c>
       <c r="AM110" s="8"/>
       <c r="AN110" s="8"/>
       <c r="AO110" s="8"/>
@@ -20493,11 +20818,11 @@
         <v>150</v>
       </c>
       <c r="L111" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-2</v>
       </c>
       <c r="M111" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>148</v>
       </c>
       <c r="N111" s="8"/>
@@ -20506,7 +20831,7 @@
       </c>
       <c r="P111" s="8"/>
       <c r="Q111" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>29.6</v>
       </c>
       <c r="R111" s="4">
@@ -20514,11 +20839,11 @@
         <v>254.40000000000003</v>
       </c>
       <c r="S111" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>254</v>
       </c>
       <c r="T111" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>152</v>
       </c>
       <c r="U111" s="4">
@@ -20527,11 +20852,11 @@
       </c>
       <c r="V111" s="19"/>
       <c r="W111" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>13.986486486486486</v>
       </c>
       <c r="X111" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>5.4054054054054053</v>
       </c>
       <c r="Y111" s="8">
@@ -20566,14 +20891,17 @@
       </c>
       <c r="AI111" s="8"/>
       <c r="AJ111" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>50.160000000000004</v>
       </c>
       <c r="AK111" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>33.660000000000004</v>
       </c>
-      <c r="AL111" s="8"/>
+      <c r="AL111" s="8">
+        <f t="shared" si="44"/>
+        <v>9.7680000000000007</v>
+      </c>
       <c r="AM111" s="8"/>
       <c r="AN111" s="8"/>
       <c r="AO111" s="8"/>
@@ -20617,11 +20945,11 @@
         <v>30</v>
       </c>
       <c r="L112" s="11">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-30</v>
       </c>
       <c r="M112" s="11">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="N112" s="11"/>
@@ -20630,26 +20958,26 @@
       </c>
       <c r="P112" s="11"/>
       <c r="Q112" s="11">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="R112" s="14"/>
       <c r="S112" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T112" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U112" s="4"/>
       <c r="V112" s="19"/>
       <c r="W112" s="8" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X112" s="11" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y112" s="11">
@@ -20684,14 +21012,17 @@
       </c>
       <c r="AI112" s="11"/>
       <c r="AJ112" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AK112" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL112" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL112" s="8">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
       <c r="AM112" s="8"/>
       <c r="AN112" s="8"/>
       <c r="AO112" s="8"/>
@@ -20739,11 +21070,11 @@
         <v>434</v>
       </c>
       <c r="L113" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-167</v>
       </c>
       <c r="M113" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>237</v>
       </c>
       <c r="N113" s="8">
@@ -20754,7 +21085,7 @@
       </c>
       <c r="P113" s="8"/>
       <c r="Q113" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>47.4</v>
       </c>
       <c r="R113" s="4">
@@ -20762,11 +21093,11 @@
         <v>425.19999999999993</v>
       </c>
       <c r="S113" s="4">
-        <f t="shared" ref="S113:S115" si="57">V113</f>
+        <f t="shared" ref="S113:S115" si="59">V113</f>
         <v>440</v>
       </c>
       <c r="T113" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>264</v>
       </c>
       <c r="U113" s="4">
@@ -20778,11 +21109,11 @@
         <v>440</v>
       </c>
       <c r="W113" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>13.312236286919832</v>
       </c>
       <c r="X113" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>4.0295358649789028</v>
       </c>
       <c r="Y113" s="8">
@@ -20817,14 +21148,17 @@
       </c>
       <c r="AI113" s="8"/>
       <c r="AJ113" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>26.400000000000002</v>
       </c>
       <c r="AK113" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>17.600000000000001</v>
       </c>
-      <c r="AL113" s="8"/>
+      <c r="AL113" s="8">
+        <f t="shared" si="44"/>
+        <v>4.74</v>
+      </c>
       <c r="AM113" s="8"/>
       <c r="AN113" s="8"/>
       <c r="AO113" s="8"/>
@@ -20872,11 +21206,11 @@
         <v>265</v>
       </c>
       <c r="L114" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-35</v>
       </c>
       <c r="M114" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>210</v>
       </c>
       <c r="N114" s="8">
@@ -20889,19 +21223,19 @@
         <v>160</v>
       </c>
       <c r="Q114" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>42</v>
       </c>
       <c r="R114" s="4">
-        <f t="shared" ref="R114:R115" si="58">15*Q114-P114-O114-F114</f>
+        <f t="shared" ref="R114:R115" si="60">15*Q114-P114-O114-F114</f>
         <v>63</v>
       </c>
       <c r="S114" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>90</v>
       </c>
       <c r="T114" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>90</v>
       </c>
       <c r="U114" s="4"/>
@@ -20910,11 +21244,11 @@
         <v>90</v>
       </c>
       <c r="W114" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>15.642857142857142</v>
       </c>
       <c r="X114" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>13.5</v>
       </c>
       <c r="Y114" s="8">
@@ -20951,14 +21285,17 @@
         <v>173</v>
       </c>
       <c r="AJ114" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>9</v>
       </c>
       <c r="AK114" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL114" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL114" s="8">
+        <f t="shared" si="44"/>
+        <v>4.2</v>
+      </c>
       <c r="AM114" s="8"/>
       <c r="AN114" s="8"/>
       <c r="AO114" s="8"/>
@@ -21006,11 +21343,11 @@
         <v>694</v>
       </c>
       <c r="L115" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-270</v>
       </c>
       <c r="M115" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>392</v>
       </c>
       <c r="N115" s="8">
@@ -21021,19 +21358,19 @@
       </c>
       <c r="P115" s="8"/>
       <c r="Q115" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>78.400000000000006</v>
       </c>
       <c r="R115" s="4">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>429</v>
       </c>
       <c r="S115" s="4">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>450</v>
       </c>
       <c r="T115" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>270</v>
       </c>
       <c r="U115" s="4">
@@ -21045,11 +21382,11 @@
         <v>450</v>
       </c>
       <c r="W115" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>15.267857142857142</v>
       </c>
       <c r="X115" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>9.5280612244897949</v>
       </c>
       <c r="Y115" s="8">
@@ -21086,14 +21423,17 @@
         <v>175</v>
       </c>
       <c r="AJ115" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>108</v>
       </c>
       <c r="AK115" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>72</v>
       </c>
-      <c r="AL115" s="8"/>
+      <c r="AL115" s="8">
+        <f t="shared" si="44"/>
+        <v>31.360000000000003</v>
+      </c>
       <c r="AM115" s="8"/>
       <c r="AN115" s="8"/>
       <c r="AO115" s="8"/>
@@ -21139,11 +21479,11 @@
         <v>17</v>
       </c>
       <c r="L116" s="11">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-19</v>
       </c>
       <c r="M116" s="11">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>-2</v>
       </c>
       <c r="N116" s="11"/>
@@ -21152,26 +21492,26 @@
       </c>
       <c r="P116" s="11"/>
       <c r="Q116" s="11">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>-0.4</v>
       </c>
       <c r="R116" s="14"/>
       <c r="S116" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T116" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U116" s="4"/>
       <c r="V116" s="19"/>
       <c r="W116" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="X116" s="11">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="Y116" s="11">
@@ -21208,14 +21548,17 @@
         <v>178</v>
       </c>
       <c r="AJ116" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AK116" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL116" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL116" s="8">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
       <c r="AM116" s="8"/>
       <c r="AN116" s="8"/>
       <c r="AO116" s="8"/>
@@ -21257,11 +21600,11 @@
       <c r="J117" s="8"/>
       <c r="K117" s="8"/>
       <c r="L117" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="M117" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="N117" s="8"/>
@@ -21271,26 +21614,26 @@
       </c>
       <c r="P117" s="8"/>
       <c r="Q117" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="R117" s="4"/>
       <c r="S117" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T117" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U117" s="4"/>
       <c r="V117" s="19"/>
       <c r="W117" s="8" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X117" s="8" t="e">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Y117" s="8">
@@ -21327,14 +21670,17 @@
         <v>180</v>
       </c>
       <c r="AJ117" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AK117" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL117" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL117" s="8">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
       <c r="AM117" s="8"/>
       <c r="AN117" s="8"/>
       <c r="AO117" s="8"/>
@@ -21382,11 +21728,11 @@
         <v>29</v>
       </c>
       <c r="L118" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-1</v>
       </c>
       <c r="M118" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>28</v>
       </c>
       <c r="N118" s="8"/>
@@ -21395,29 +21741,29 @@
       </c>
       <c r="P118" s="8"/>
       <c r="Q118" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>5.6</v>
       </c>
       <c r="R118" s="4">
-        <f t="shared" ref="R118:R122" si="59">15*Q118-P118-O118-F118</f>
+        <f t="shared" ref="R118:R122" si="61">15*Q118-P118-O118-F118</f>
         <v>7</v>
       </c>
       <c r="S118" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>7</v>
       </c>
       <c r="T118" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>7</v>
       </c>
       <c r="U118" s="4"/>
       <c r="V118" s="19"/>
       <c r="W118" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>15.000000000000002</v>
       </c>
       <c r="X118" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>13.75</v>
       </c>
       <c r="Y118" s="8">
@@ -21454,14 +21800,17 @@
         <v>155</v>
       </c>
       <c r="AJ118" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>2.1</v>
       </c>
       <c r="AK118" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL118" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL118" s="8">
+        <f t="shared" si="44"/>
+        <v>1.68</v>
+      </c>
       <c r="AM118" s="8"/>
       <c r="AN118" s="8"/>
       <c r="AO118" s="8"/>
@@ -21510,11 +21859,11 @@
         <v>227</v>
       </c>
       <c r="L119" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-132</v>
       </c>
       <c r="M119" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>95</v>
       </c>
       <c r="N119" s="8"/>
@@ -21523,29 +21872,29 @@
       </c>
       <c r="P119" s="8"/>
       <c r="Q119" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>19</v>
       </c>
       <c r="R119" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>75</v>
       </c>
       <c r="S119" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>75</v>
       </c>
       <c r="T119" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>75</v>
       </c>
       <c r="U119" s="4"/>
       <c r="V119" s="19"/>
       <c r="W119" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>15</v>
       </c>
       <c r="X119" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>11.052631578947368</v>
       </c>
       <c r="Y119" s="8">
@@ -21582,14 +21931,17 @@
         <v>182</v>
       </c>
       <c r="AJ119" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>22.5</v>
       </c>
       <c r="AK119" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL119" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL119" s="8">
+        <f t="shared" si="44"/>
+        <v>5.7</v>
+      </c>
       <c r="AM119" s="8"/>
       <c r="AN119" s="8"/>
       <c r="AO119" s="8"/>
@@ -21637,11 +21989,11 @@
         <v>18</v>
       </c>
       <c r="L120" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="M120" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>18</v>
       </c>
       <c r="N120" s="8"/>
@@ -21650,7 +22002,7 @@
       </c>
       <c r="P120" s="8"/>
       <c r="Q120" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>3.6</v>
       </c>
       <c r="R120" s="4"/>
@@ -21658,7 +22010,7 @@
         <v>40</v>
       </c>
       <c r="T120" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>40</v>
       </c>
       <c r="U120" s="21"/>
@@ -21667,11 +22019,11 @@
         <v>80</v>
       </c>
       <c r="W120" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>42.222222222222221</v>
       </c>
       <c r="X120" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>31.111111111111111</v>
       </c>
       <c r="Y120" s="8">
@@ -21708,14 +22060,17 @@
         <v>189</v>
       </c>
       <c r="AJ120" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>4</v>
       </c>
       <c r="AK120" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL120" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL120" s="8">
+        <f t="shared" si="44"/>
+        <v>0.36000000000000004</v>
+      </c>
       <c r="AM120" s="8"/>
       <c r="AN120" s="8"/>
       <c r="AO120" s="8"/>
@@ -21764,11 +22119,11 @@
         <v>19</v>
       </c>
       <c r="L121" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-3</v>
       </c>
       <c r="M121" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>16</v>
       </c>
       <c r="N121" s="8"/>
@@ -21777,7 +22132,7 @@
       </c>
       <c r="P121" s="8"/>
       <c r="Q121" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>3.2</v>
       </c>
       <c r="R121" s="4"/>
@@ -21785,7 +22140,7 @@
         <v>40</v>
       </c>
       <c r="T121" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>40</v>
       </c>
       <c r="U121" s="21"/>
@@ -21794,11 +22149,11 @@
         <v>80</v>
       </c>
       <c r="W121" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>47.1875</v>
       </c>
       <c r="X121" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>34.6875</v>
       </c>
       <c r="Y121" s="8">
@@ -21835,14 +22190,17 @@
         <v>190</v>
       </c>
       <c r="AJ121" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>4</v>
       </c>
       <c r="AK121" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL121" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL121" s="8">
+        <f t="shared" si="44"/>
+        <v>0.32000000000000006</v>
+      </c>
       <c r="AM121" s="8"/>
       <c r="AN121" s="8"/>
       <c r="AO121" s="8"/>
@@ -21888,11 +22246,11 @@
       <c r="J122" s="8"/>
       <c r="K122" s="8"/>
       <c r="L122" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>13.916</v>
       </c>
       <c r="M122" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>13.916</v>
       </c>
       <c r="N122" s="8"/>
@@ -21902,29 +22260,29 @@
       </c>
       <c r="P122" s="8"/>
       <c r="Q122" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>2.7831999999999999</v>
       </c>
       <c r="R122" s="4">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>5.9499999999999975</v>
       </c>
       <c r="S122" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>6</v>
       </c>
       <c r="T122" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>6</v>
       </c>
       <c r="U122" s="4"/>
       <c r="V122" s="19"/>
       <c r="W122" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>15.017964932451855</v>
       </c>
       <c r="X122" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>12.862173038229377</v>
       </c>
       <c r="Y122" s="8">
@@ -21961,14 +22319,17 @@
         <v>184</v>
       </c>
       <c r="AJ122" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>6</v>
       </c>
       <c r="AK122" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL122" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL122" s="8">
+        <f t="shared" si="44"/>
+        <v>2.7831999999999999</v>
+      </c>
       <c r="AM122" s="8"/>
       <c r="AN122" s="8"/>
       <c r="AO122" s="8"/>
@@ -22016,11 +22377,11 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="L123" s="8">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>-0.13199999999999967</v>
       </c>
       <c r="M123" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>3.968</v>
       </c>
       <c r="N123" s="8"/>
@@ -22029,26 +22390,26 @@
       </c>
       <c r="P123" s="8"/>
       <c r="Q123" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.79359999999999997</v>
       </c>
       <c r="R123" s="4"/>
       <c r="S123" s="4">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T123" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U123" s="4"/>
       <c r="V123" s="19"/>
       <c r="W123" s="8">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>35.618699596774192</v>
       </c>
       <c r="X123" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>35.618699596774192</v>
       </c>
       <c r="Y123" s="8">
@@ -22085,14 +22446,17 @@
         <v>191</v>
       </c>
       <c r="AJ123" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AK123" s="8">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AL123" s="8"/>
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="AL123" s="8">
+        <f t="shared" si="44"/>
+        <v>0.79359999999999997</v>
+      </c>
       <c r="AM123" s="8"/>
       <c r="AN123" s="8"/>
       <c r="AO123" s="8"/>
